--- a/Gas_current.xlsx
+++ b/Gas_current.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="V:\Information Management\Info Sharing and Tracking\Product Services\Operations\Product Creation\ST3\ST3s_Report_Prep\All_Pages_Content_Update\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E86DDF4B-E399-48CC-AF34-D834F89430A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D46289B6-91E4-4DEC-8413-274A2BF27BA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3420" yWindow="1560" windowWidth="21600" windowHeight="9105" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-19310" yWindow="1390" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Documentation" sheetId="20" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="214">
   <si>
     <t>Saskatchewan</t>
   </si>
@@ -736,7 +736,7 @@
     <t>2025</t>
   </si>
   <si>
-    <t xml:space="preserve"> Run Date:  28 May 2025</t>
+    <t xml:space="preserve"> Run Date:  29 December 2025</t>
   </si>
 </sst>
 </file>
@@ -744,10 +744,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="#,##0.0"/>
-    <numFmt numFmtId="166" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="167" formatCode="0.0%"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="#,##0.0"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
   <fonts count="23" x14ac:knownFonts="1">
     <font>
@@ -1097,7 +1097,7 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="103">
@@ -1113,19 +1113,19 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="3"/>
     </xf>
@@ -1135,28 +1135,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="6"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="3"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1224,13 +1224,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1239,7 +1239,7 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1247,7 +1247,7 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="19" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1266,21 +1266,21 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="3"/>
     </xf>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="3"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="6"/>
     </xf>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="6"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1303,16 +1303,16 @@
     <xf numFmtId="2" fontId="15" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1409,7 +1409,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>1676400</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>33926</xdr:rowOff>
+      <xdr:rowOff>35196</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4124,25 +4124,25 @@
         <v>602088.4</v>
       </c>
       <c r="H7" s="11">
-        <v>0</v>
+        <v>560422.40000000002</v>
       </c>
       <c r="I7" s="11">
-        <v>0</v>
+        <v>584174.69999999995</v>
       </c>
       <c r="J7" s="11">
-        <v>0</v>
+        <v>554598.1</v>
       </c>
       <c r="K7" s="11">
-        <v>0</v>
+        <v>550349.5</v>
       </c>
       <c r="L7" s="11">
-        <v>0</v>
+        <v>582174.30000000005</v>
       </c>
       <c r="M7" s="11">
-        <v>0</v>
+        <v>558697.19999999995</v>
       </c>
       <c r="N7" s="11">
-        <v>0</v>
+        <v>554102</v>
       </c>
       <c r="O7" s="11">
         <v>0</v>
@@ -4182,44 +4182,44 @@
       </c>
       <c r="C10" s="13"/>
       <c r="D10" s="11">
-        <v>11601396.4</v>
+        <v>11596020.6</v>
       </c>
       <c r="E10" s="11">
-        <v>10227187.800000001</v>
+        <v>10229168.199999999</v>
       </c>
       <c r="F10" s="11">
-        <v>11696844.1</v>
+        <v>11696781.800000001</v>
       </c>
       <c r="G10" s="11">
-        <v>11238023.1</v>
+        <v>11239507.4</v>
       </c>
       <c r="H10" s="11">
-        <v>0</v>
+        <v>11398845.199999999</v>
       </c>
       <c r="I10" s="11">
-        <v>0</v>
+        <v>10672542.699999999</v>
       </c>
       <c r="J10" s="11">
-        <v>0</v>
+        <v>11248025</v>
       </c>
       <c r="K10" s="11">
-        <v>0</v>
+        <v>11200434.199999999</v>
       </c>
       <c r="L10" s="11">
-        <v>0</v>
+        <v>10849935.9</v>
       </c>
       <c r="M10" s="11">
-        <v>0</v>
+        <v>11492513.4</v>
       </c>
       <c r="N10" s="11">
-        <v>0</v>
+        <v>11507511.6</v>
       </c>
       <c r="O10" s="11">
         <v>0</v>
       </c>
       <c r="P10" s="6"/>
       <c r="Q10" s="6">
-        <v>44763451.400000006</v>
+        <v>123131286.00000001</v>
       </c>
     </row>
     <row r="11" spans="2:17" x14ac:dyDescent="0.25">
@@ -4228,44 +4228,44 @@
       </c>
       <c r="C11" s="13"/>
       <c r="D11" s="11">
-        <v>355873.6</v>
+        <v>356370.3</v>
       </c>
       <c r="E11" s="11">
-        <v>311583.8</v>
+        <v>312054.09999999998</v>
       </c>
       <c r="F11" s="11">
-        <v>339128.7</v>
+        <v>340220.8</v>
       </c>
       <c r="G11" s="11">
-        <v>297582.5</v>
+        <v>298419.8</v>
       </c>
       <c r="H11" s="11">
-        <v>0</v>
+        <v>263142.59999999998</v>
       </c>
       <c r="I11" s="11">
-        <v>0</v>
+        <v>252787.1</v>
       </c>
       <c r="J11" s="11">
-        <v>0</v>
+        <v>341507</v>
       </c>
       <c r="K11" s="11">
-        <v>0</v>
+        <v>327952.2</v>
       </c>
       <c r="L11" s="11">
-        <v>0</v>
+        <v>331771.3</v>
       </c>
       <c r="M11" s="11">
-        <v>0</v>
+        <v>346804.6</v>
       </c>
       <c r="N11" s="11">
-        <v>0</v>
+        <v>339251.8</v>
       </c>
       <c r="O11" s="11">
         <v>0</v>
       </c>
       <c r="P11" s="6"/>
       <c r="Q11" s="6">
-        <v>1304168.5999999999</v>
+        <v>3510281.6</v>
       </c>
     </row>
     <row r="12" spans="2:17" x14ac:dyDescent="0.25">
@@ -4292,44 +4292,44 @@
       </c>
       <c r="C13" s="13"/>
       <c r="D13" s="11">
-        <v>1253348.3</v>
+        <v>1253341.2</v>
       </c>
       <c r="E13" s="11">
-        <v>1728736.5</v>
+        <v>1728732.4</v>
       </c>
       <c r="F13" s="11">
-        <v>539355.9</v>
+        <v>539600.9</v>
       </c>
       <c r="G13" s="11">
         <v>133377.70000000001</v>
       </c>
       <c r="H13" s="11">
-        <v>0</v>
+        <v>2996.2</v>
       </c>
       <c r="I13" s="11">
-        <v>0</v>
+        <v>719.1</v>
       </c>
       <c r="J13" s="11">
-        <v>0</v>
+        <v>739.5</v>
       </c>
       <c r="K13" s="11">
-        <v>0</v>
+        <v>14338.3</v>
       </c>
       <c r="L13" s="11">
-        <v>0</v>
+        <v>10088.6</v>
       </c>
       <c r="M13" s="11">
-        <v>0</v>
+        <v>72634.2</v>
       </c>
       <c r="N13" s="11">
-        <v>0</v>
+        <v>337876.8</v>
       </c>
       <c r="O13" s="11">
         <v>0</v>
       </c>
       <c r="P13" s="6"/>
       <c r="Q13" s="6">
-        <v>3654818.4</v>
+        <v>4094444.9</v>
       </c>
     </row>
     <row r="14" spans="2:17" x14ac:dyDescent="0.25">
@@ -4338,44 +4338,44 @@
       </c>
       <c r="C14" s="13"/>
       <c r="D14" s="11">
-        <v>-7209</v>
+        <v>-7188.8</v>
       </c>
       <c r="E14" s="11">
-        <v>-16058.9</v>
+        <v>-16041.7</v>
       </c>
       <c r="F14" s="11">
-        <v>-58633.7</v>
+        <v>-58359.5</v>
       </c>
       <c r="G14" s="11">
         <v>-797789.3</v>
       </c>
       <c r="H14" s="11">
-        <v>0</v>
+        <v>-1408423</v>
       </c>
       <c r="I14" s="11">
-        <v>0</v>
+        <v>-733629.6</v>
       </c>
       <c r="J14" s="11">
-        <v>0</v>
+        <v>-813842.2</v>
       </c>
       <c r="K14" s="11">
-        <v>0</v>
+        <v>-651209.9</v>
       </c>
       <c r="L14" s="11">
-        <v>0</v>
+        <v>-677808.4</v>
       </c>
       <c r="M14" s="11">
-        <v>0</v>
+        <v>-329748.90000000002</v>
       </c>
       <c r="N14" s="11">
-        <v>0</v>
+        <v>-117125.5</v>
       </c>
       <c r="O14" s="11">
         <v>0</v>
       </c>
       <c r="P14" s="6"/>
       <c r="Q14" s="6">
-        <v>-879690.9</v>
+        <v>-5611166.8000000007</v>
       </c>
     </row>
     <row r="15" spans="2:17" x14ac:dyDescent="0.25">
@@ -4396,32 +4396,32 @@
         <v>861.7</v>
       </c>
       <c r="H15" s="11">
-        <v>0</v>
+        <v>1004.5</v>
       </c>
       <c r="I15" s="11">
-        <v>0</v>
+        <v>756.1</v>
       </c>
       <c r="J15" s="11">
-        <v>0</v>
+        <v>675.6</v>
       </c>
       <c r="K15" s="11">
-        <v>0</v>
+        <v>682.8</v>
       </c>
       <c r="L15" s="11">
-        <v>0</v>
+        <v>596.4</v>
       </c>
       <c r="M15" s="11">
-        <v>0</v>
+        <v>936.1</v>
       </c>
       <c r="N15" s="11">
-        <v>0</v>
+        <v>541.4</v>
       </c>
       <c r="O15" s="11">
         <v>0</v>
       </c>
       <c r="P15" s="6"/>
       <c r="Q15" s="6">
-        <v>4134.0999999999995</v>
+        <v>9327</v>
       </c>
     </row>
     <row r="16" spans="2:17" x14ac:dyDescent="0.25">
@@ -4433,7 +4433,7 @@
         <v>-8508.1</v>
       </c>
       <c r="E16" s="11">
-        <v>-9018.7000000000007</v>
+        <v>-9013.1</v>
       </c>
       <c r="F16" s="11">
         <v>-10576.2</v>
@@ -4442,32 +4442,32 @@
         <v>-11193.9</v>
       </c>
       <c r="H16" s="11">
-        <v>0</v>
+        <v>-11171.7</v>
       </c>
       <c r="I16" s="11">
-        <v>0</v>
+        <v>-10973</v>
       </c>
       <c r="J16" s="11">
-        <v>0</v>
+        <v>-12073.3</v>
       </c>
       <c r="K16" s="11">
-        <v>0</v>
+        <v>-12176.6</v>
       </c>
       <c r="L16" s="11">
-        <v>0</v>
+        <v>-42951.6</v>
       </c>
       <c r="M16" s="11">
-        <v>0</v>
+        <v>-23493.599999999999</v>
       </c>
       <c r="N16" s="11">
-        <v>0</v>
+        <v>-14008.1</v>
       </c>
       <c r="O16" s="11">
         <v>0</v>
       </c>
       <c r="P16" s="6"/>
       <c r="Q16" s="6">
-        <v>-39296.9</v>
+        <v>-166139.20000000001</v>
       </c>
     </row>
     <row r="17" spans="2:17" x14ac:dyDescent="0.25">
@@ -4494,44 +4494,44 @@
       </c>
       <c r="C18" s="13"/>
       <c r="D18" s="11">
-        <v>13195914.300000001</v>
+        <v>13191048.299999999</v>
       </c>
       <c r="E18" s="11">
-        <v>12243462.600000001</v>
+        <v>12245932</v>
       </c>
       <c r="F18" s="11">
-        <v>12507346</v>
+        <v>12508895.000000002</v>
       </c>
       <c r="G18" s="11">
-        <v>10860861.799999997</v>
+        <v>10863183.399999999</v>
       </c>
       <c r="H18" s="11">
-        <v>0</v>
+        <v>10246393.799999999</v>
       </c>
       <c r="I18" s="11">
-        <v>0</v>
+        <v>10182202.399999999</v>
       </c>
       <c r="J18" s="11">
-        <v>0</v>
+        <v>10765031.6</v>
       </c>
       <c r="K18" s="11">
-        <v>0</v>
+        <v>10880021</v>
       </c>
       <c r="L18" s="11">
-        <v>0</v>
+        <v>10471632.200000001</v>
       </c>
       <c r="M18" s="11">
-        <v>0</v>
+        <v>11559645.799999999</v>
       </c>
       <c r="N18" s="11">
-        <v>0</v>
+        <v>12054048.000000002</v>
       </c>
       <c r="O18" s="11">
         <v>0</v>
       </c>
       <c r="P18" s="6"/>
       <c r="Q18" s="11">
-        <v>48807584.70000001</v>
+        <v>124968033.50000001</v>
       </c>
     </row>
     <row r="19" spans="2:17" x14ac:dyDescent="0.25">
@@ -4558,44 +4558,44 @@
       </c>
       <c r="C20" s="13"/>
       <c r="D20" s="11">
-        <v>573865.30000000005</v>
+        <v>573932.5</v>
       </c>
       <c r="E20" s="11">
-        <v>484699.1</v>
+        <v>484605.7</v>
       </c>
       <c r="F20" s="11">
-        <v>548983.30000000005</v>
+        <v>548636.80000000005</v>
       </c>
       <c r="G20" s="11">
-        <v>476709.3</v>
+        <v>476581.5</v>
       </c>
       <c r="H20" s="11">
-        <v>0</v>
+        <v>372668.2</v>
       </c>
       <c r="I20" s="11">
-        <v>0</v>
+        <v>458505.4</v>
       </c>
       <c r="J20" s="11">
-        <v>0</v>
+        <v>506729.7</v>
       </c>
       <c r="K20" s="11">
-        <v>0</v>
+        <v>513144.6</v>
       </c>
       <c r="L20" s="11">
-        <v>0</v>
+        <v>498371.1</v>
       </c>
       <c r="M20" s="11">
-        <v>0</v>
+        <v>527511.6</v>
       </c>
       <c r="N20" s="11">
-        <v>0</v>
+        <v>539172.6</v>
       </c>
       <c r="O20" s="11">
         <v>0</v>
       </c>
       <c r="P20" s="6"/>
       <c r="Q20" s="6">
-        <v>2084257</v>
+        <v>5499859.6999999993</v>
       </c>
     </row>
     <row r="21" spans="2:17" x14ac:dyDescent="0.25">
@@ -4616,32 +4616,32 @@
         <v>353772.79999999999</v>
       </c>
       <c r="H21" s="9">
-        <v>0</v>
+        <v>389887.2</v>
       </c>
       <c r="I21" s="9">
-        <v>0</v>
+        <v>268396.7</v>
       </c>
       <c r="J21" s="9">
-        <v>0</v>
+        <v>386665.4</v>
       </c>
       <c r="K21" s="9">
-        <v>0</v>
+        <v>364574.8</v>
       </c>
       <c r="L21" s="9">
-        <v>0</v>
+        <v>352404.9</v>
       </c>
       <c r="M21" s="9">
-        <v>0</v>
+        <v>374988.79999999999</v>
       </c>
       <c r="N21" s="9">
-        <v>0</v>
+        <v>351740</v>
       </c>
       <c r="O21" s="9">
         <v>0</v>
       </c>
       <c r="P21" s="6"/>
       <c r="Q21" s="7">
-        <v>1400361.7</v>
+        <v>3889019.4999999995</v>
       </c>
     </row>
     <row r="22" spans="2:17" x14ac:dyDescent="0.25">
@@ -4650,44 +4650,44 @@
       </c>
       <c r="C22" s="14"/>
       <c r="D22" s="11">
-        <v>14129806.700000001</v>
+        <v>14125007.899999999</v>
       </c>
       <c r="E22" s="11">
-        <v>13051867.300000001</v>
+        <v>13054243.299999999</v>
       </c>
       <c r="F22" s="11">
-        <v>13419185.5</v>
+        <v>13420388.000000002</v>
       </c>
       <c r="G22" s="11">
-        <v>11691343.899999999</v>
+        <v>11693537.699999999</v>
       </c>
       <c r="H22" s="11">
-        <v>0</v>
+        <v>11008949.199999997</v>
       </c>
       <c r="I22" s="11">
-        <v>0</v>
+        <v>10909104.499999998</v>
       </c>
       <c r="J22" s="11">
-        <v>0</v>
+        <v>11658426.699999999</v>
       </c>
       <c r="K22" s="11">
-        <v>0</v>
+        <v>11757740.4</v>
       </c>
       <c r="L22" s="11">
-        <v>0</v>
+        <v>11322408.200000001</v>
       </c>
       <c r="M22" s="11">
-        <v>0</v>
+        <v>12462146.199999999</v>
       </c>
       <c r="N22" s="11">
-        <v>0</v>
+        <v>12944960.600000001</v>
       </c>
       <c r="O22" s="11">
         <v>0</v>
       </c>
       <c r="P22" s="6"/>
       <c r="Q22" s="11">
-        <v>52292203.400000013</v>
+        <v>134356912.70000002</v>
       </c>
     </row>
     <row r="23" spans="2:17" x14ac:dyDescent="0.25">
@@ -4734,44 +4734,44 @@
       </c>
       <c r="C25" s="13"/>
       <c r="D25" s="11">
-        <v>881.3</v>
+        <v>881.5</v>
       </c>
       <c r="E25" s="11">
-        <v>619.29999999999995</v>
+        <v>619.5</v>
       </c>
       <c r="F25" s="11">
-        <v>761.9</v>
+        <v>759.2</v>
       </c>
       <c r="G25" s="11">
-        <v>721</v>
+        <v>729.4</v>
       </c>
       <c r="H25" s="11">
-        <v>0</v>
+        <v>776.4</v>
       </c>
       <c r="I25" s="11">
-        <v>0</v>
+        <v>657.2</v>
       </c>
       <c r="J25" s="11">
-        <v>0</v>
+        <v>677.2</v>
       </c>
       <c r="K25" s="11">
-        <v>0</v>
+        <v>749.1</v>
       </c>
       <c r="L25" s="11">
-        <v>0</v>
+        <v>636.1</v>
       </c>
       <c r="M25" s="11">
-        <v>0</v>
+        <v>761.7</v>
       </c>
       <c r="N25" s="11">
-        <v>0</v>
+        <v>732.3</v>
       </c>
       <c r="O25" s="11">
         <v>0</v>
       </c>
       <c r="P25" s="6"/>
       <c r="Q25" s="6">
-        <v>2983.5</v>
+        <v>7979.6</v>
       </c>
     </row>
     <row r="26" spans="2:17" x14ac:dyDescent="0.25">
@@ -4792,32 +4792,32 @@
         <v>47223.7</v>
       </c>
       <c r="H26" s="11">
-        <v>0</v>
+        <v>51254.9</v>
       </c>
       <c r="I26" s="11">
-        <v>0</v>
+        <v>46206</v>
       </c>
       <c r="J26" s="11">
-        <v>0</v>
+        <v>52589.599999999999</v>
       </c>
       <c r="K26" s="11">
-        <v>0</v>
+        <v>51284.4</v>
       </c>
       <c r="L26" s="11">
-        <v>0</v>
+        <v>44648.7</v>
       </c>
       <c r="M26" s="11">
-        <v>0</v>
+        <v>48903.6</v>
       </c>
       <c r="N26" s="11">
-        <v>0</v>
+        <v>48823.3</v>
       </c>
       <c r="O26" s="11">
         <v>0</v>
       </c>
       <c r="P26" s="6"/>
       <c r="Q26" s="6">
-        <v>197626</v>
+        <v>541336.5</v>
       </c>
     </row>
     <row r="27" spans="2:17" x14ac:dyDescent="0.25">
@@ -4826,44 +4826,44 @@
       </c>
       <c r="C27" s="13"/>
       <c r="D27" s="11">
-        <v>259983.7</v>
+        <v>260009.8</v>
       </c>
       <c r="E27" s="11">
-        <v>238238.1</v>
+        <v>237311.6</v>
       </c>
       <c r="F27" s="11">
-        <v>274520</v>
+        <v>270775</v>
       </c>
       <c r="G27" s="11">
-        <v>238031.9</v>
+        <v>236868.3</v>
       </c>
       <c r="H27" s="11">
-        <v>0</v>
+        <v>208446</v>
       </c>
       <c r="I27" s="11">
-        <v>0</v>
+        <v>215926.6</v>
       </c>
       <c r="J27" s="11">
-        <v>0</v>
+        <v>201170.3</v>
       </c>
       <c r="K27" s="11">
-        <v>0</v>
+        <v>206830.3</v>
       </c>
       <c r="L27" s="11">
-        <v>0</v>
+        <v>253291</v>
       </c>
       <c r="M27" s="11">
-        <v>0</v>
+        <v>245001.7</v>
       </c>
       <c r="N27" s="11">
-        <v>0</v>
+        <v>252749.2</v>
       </c>
       <c r="O27" s="11">
         <v>0</v>
       </c>
       <c r="P27" s="6"/>
       <c r="Q27" s="6">
-        <v>1010773.7000000001</v>
+        <v>2588379.8000000003</v>
       </c>
     </row>
     <row r="28" spans="2:17" x14ac:dyDescent="0.25">
@@ -4881,35 +4881,35 @@
         <v>620929.69999999995</v>
       </c>
       <c r="G28" s="11">
-        <v>529726.1</v>
+        <v>529528.4</v>
       </c>
       <c r="H28" s="11">
-        <v>0</v>
+        <v>497696.1</v>
       </c>
       <c r="I28" s="11">
-        <v>0</v>
+        <v>526066.6</v>
       </c>
       <c r="J28" s="11">
-        <v>0</v>
+        <v>482904.3</v>
       </c>
       <c r="K28" s="11">
-        <v>0</v>
+        <v>502901.2</v>
       </c>
       <c r="L28" s="11">
-        <v>0</v>
+        <v>464742.40000000002</v>
       </c>
       <c r="M28" s="11">
-        <v>0</v>
+        <v>546841.59999999998</v>
       </c>
       <c r="N28" s="11">
-        <v>0</v>
+        <v>593740.6</v>
       </c>
       <c r="O28" s="11">
         <v>0</v>
       </c>
       <c r="P28" s="6"/>
       <c r="Q28" s="6">
-        <v>2361752.6999999997</v>
+        <v>5976447.7999999998</v>
       </c>
     </row>
     <row r="29" spans="2:17" x14ac:dyDescent="0.25">
@@ -4918,44 +4918,44 @@
       </c>
       <c r="C29" s="13"/>
       <c r="D29" s="11">
-        <v>134379.70000000001</v>
+        <v>134615.9</v>
       </c>
       <c r="E29" s="11">
-        <v>126016.4</v>
+        <v>126886</v>
       </c>
       <c r="F29" s="11">
-        <v>134594.4</v>
+        <v>134416.5</v>
       </c>
       <c r="G29" s="11">
-        <v>123308.3</v>
+        <v>123964.8</v>
       </c>
       <c r="H29" s="11">
-        <v>0</v>
+        <v>116987.3</v>
       </c>
       <c r="I29" s="11">
-        <v>0</v>
+        <v>85521.4</v>
       </c>
       <c r="J29" s="11">
-        <v>0</v>
+        <v>64180.800000000003</v>
       </c>
       <c r="K29" s="11">
-        <v>0</v>
+        <v>85770.2</v>
       </c>
       <c r="L29" s="11">
-        <v>0</v>
+        <v>116351.2</v>
       </c>
       <c r="M29" s="11">
-        <v>0</v>
+        <v>119156</v>
       </c>
       <c r="N29" s="11">
-        <v>0</v>
+        <v>130881</v>
       </c>
       <c r="O29" s="11">
         <v>0</v>
       </c>
       <c r="P29" s="6"/>
       <c r="Q29" s="6">
-        <v>518298.8</v>
+        <v>1238731.1000000001</v>
       </c>
     </row>
     <row r="30" spans="2:17" x14ac:dyDescent="0.25">
@@ -4973,35 +4973,35 @@
         <v>3965865.7</v>
       </c>
       <c r="G30" s="9">
-        <v>3670384.2</v>
+        <v>3670374.6</v>
       </c>
       <c r="H30" s="9">
-        <v>0</v>
+        <v>4082722.8</v>
       </c>
       <c r="I30" s="9">
-        <v>0</v>
+        <v>3776468.6</v>
       </c>
       <c r="J30" s="9">
-        <v>0</v>
+        <v>3767248.7</v>
       </c>
       <c r="K30" s="9">
-        <v>0</v>
+        <v>3395940.2</v>
       </c>
       <c r="L30" s="9">
-        <v>0</v>
+        <v>2869704.5</v>
       </c>
       <c r="M30" s="64">
-        <v>0</v>
+        <v>3329549.5</v>
       </c>
       <c r="N30" s="64">
-        <v>0</v>
+        <v>3803988.8</v>
       </c>
       <c r="O30" s="64">
         <v>0</v>
       </c>
       <c r="P30" s="6"/>
       <c r="Q30" s="7">
-        <v>15523130.300000001</v>
+        <v>40548743.799999997</v>
       </c>
     </row>
     <row r="31" spans="2:17" x14ac:dyDescent="0.25">
@@ -5010,44 +5010,44 @@
       </c>
       <c r="C31" s="14"/>
       <c r="D31" s="11">
-        <v>5198265.5999999996</v>
+        <v>5198528.0999999996</v>
       </c>
       <c r="E31" s="11">
-        <v>4758863</v>
+        <v>4758806.3</v>
       </c>
       <c r="F31" s="11">
-        <v>5048041.2</v>
+        <v>5044115.5999999996</v>
       </c>
       <c r="G31" s="11">
-        <v>4609395.2</v>
+        <v>4608689.2</v>
       </c>
       <c r="H31" s="11">
-        <v>0</v>
+        <v>4957883.5</v>
       </c>
       <c r="I31" s="11">
-        <v>0</v>
+        <v>4650846.4000000004</v>
       </c>
       <c r="J31" s="11">
-        <v>0</v>
+        <v>4568770.9000000004</v>
       </c>
       <c r="K31" s="11">
-        <v>0</v>
+        <v>4243475.4000000004</v>
       </c>
       <c r="L31" s="11">
-        <v>0</v>
+        <v>3749373.9</v>
       </c>
       <c r="M31" s="11">
-        <v>0</v>
+        <v>4290214.0999999996</v>
       </c>
       <c r="N31" s="11">
-        <v>0</v>
+        <v>4830915.2</v>
       </c>
       <c r="O31" s="11">
         <v>0</v>
       </c>
       <c r="P31" s="6"/>
       <c r="Q31" s="11">
-        <v>19614565</v>
+        <v>50901618.599999994</v>
       </c>
     </row>
     <row r="32" spans="2:17" x14ac:dyDescent="0.25">
@@ -5093,44 +5093,44 @@
       </c>
       <c r="C34" s="13"/>
       <c r="D34" s="11">
-        <v>96509.7</v>
+        <v>96529.600000000006</v>
       </c>
       <c r="E34" s="11">
-        <v>92069.8</v>
+        <v>92313.7</v>
       </c>
       <c r="F34" s="11">
-        <v>96420.800000000003</v>
+        <v>96383.2</v>
       </c>
       <c r="G34" s="11">
-        <v>93590.7</v>
+        <v>93404.2</v>
       </c>
       <c r="H34" s="11">
-        <v>0</v>
+        <v>97324.800000000003</v>
       </c>
       <c r="I34" s="11">
-        <v>0</v>
+        <v>91134.1</v>
       </c>
       <c r="J34" s="11">
-        <v>0</v>
+        <v>92466.1</v>
       </c>
       <c r="K34" s="11">
-        <v>0</v>
+        <v>97158.9</v>
       </c>
       <c r="L34" s="11">
-        <v>0</v>
+        <v>93145.3</v>
       </c>
       <c r="M34" s="11">
-        <v>0</v>
+        <v>92344.4</v>
       </c>
       <c r="N34" s="11">
-        <v>0</v>
+        <v>89247.9</v>
       </c>
       <c r="O34" s="11">
         <v>0</v>
       </c>
       <c r="P34" s="6"/>
       <c r="Q34" s="6">
-        <v>378591</v>
+        <v>1031452.2000000001</v>
       </c>
     </row>
     <row r="35" spans="2:17" x14ac:dyDescent="0.25">
@@ -5139,44 +5139,44 @@
       </c>
       <c r="C35" s="13"/>
       <c r="D35" s="11">
-        <v>781443.1</v>
+        <v>781164.1</v>
       </c>
       <c r="E35" s="11">
-        <v>705441.1</v>
+        <v>707293.5</v>
       </c>
       <c r="F35" s="11">
-        <v>768966.1</v>
+        <v>770368.2</v>
       </c>
       <c r="G35" s="11">
-        <v>703372.6</v>
+        <v>705306.8</v>
       </c>
       <c r="H35" s="11">
-        <v>0</v>
+        <v>727169.3</v>
       </c>
       <c r="I35" s="11">
-        <v>0</v>
+        <v>666401.5</v>
       </c>
       <c r="J35" s="11">
-        <v>0</v>
+        <v>706323.6</v>
       </c>
       <c r="K35" s="11">
-        <v>0</v>
+        <v>697904.1</v>
       </c>
       <c r="L35" s="11">
-        <v>0</v>
+        <v>678467.8</v>
       </c>
       <c r="M35" s="11">
-        <v>0</v>
+        <v>737344</v>
       </c>
       <c r="N35" s="11">
-        <v>0</v>
+        <v>746955.6</v>
       </c>
       <c r="O35" s="11">
         <v>0</v>
       </c>
       <c r="P35" s="6"/>
       <c r="Q35" s="6">
-        <v>2959222.9</v>
+        <v>7924698.4999999981</v>
       </c>
     </row>
     <row r="36" spans="2:17" x14ac:dyDescent="0.25">
@@ -5185,44 +5185,44 @@
       </c>
       <c r="C36" s="13"/>
       <c r="D36" s="11">
-        <v>24142.799999999999</v>
+        <v>24215.3</v>
       </c>
       <c r="E36" s="11">
-        <v>21029.7</v>
+        <v>21125.200000000001</v>
       </c>
       <c r="F36" s="11">
-        <v>23104.2</v>
+        <v>23207</v>
       </c>
       <c r="G36" s="11">
-        <v>20333.2</v>
+        <v>20143.2</v>
       </c>
       <c r="H36" s="11">
-        <v>0</v>
+        <v>18998</v>
       </c>
       <c r="I36" s="11">
-        <v>0</v>
+        <v>17369.8</v>
       </c>
       <c r="J36" s="11">
-        <v>0</v>
+        <v>15759</v>
       </c>
       <c r="K36" s="11">
-        <v>0</v>
+        <v>15589.8</v>
       </c>
       <c r="L36" s="11">
-        <v>0</v>
+        <v>15385.3</v>
       </c>
       <c r="M36" s="11">
-        <v>0</v>
+        <v>18768.400000000001</v>
       </c>
       <c r="N36" s="11">
-        <v>0</v>
+        <v>18766</v>
       </c>
       <c r="O36" s="11">
         <v>0</v>
       </c>
       <c r="P36" s="6"/>
       <c r="Q36" s="6">
-        <v>88609.9</v>
+        <v>209326.99999999997</v>
       </c>
     </row>
     <row r="37" spans="2:17" x14ac:dyDescent="0.25">
@@ -5231,44 +5231,44 @@
       </c>
       <c r="C37" s="13"/>
       <c r="D37" s="9">
-        <v>834638.6</v>
+        <v>834910.9</v>
       </c>
       <c r="E37" s="9">
-        <v>729093.7</v>
+        <v>729325.8</v>
       </c>
       <c r="F37" s="9">
-        <v>833390.9</v>
+        <v>833065.2</v>
       </c>
       <c r="G37" s="9">
-        <v>800966</v>
+        <v>800732.3</v>
       </c>
       <c r="H37" s="9">
-        <v>0</v>
+        <v>796585.9</v>
       </c>
       <c r="I37" s="9">
-        <v>0</v>
+        <v>743245.2</v>
       </c>
       <c r="J37" s="9">
-        <v>0</v>
+        <v>805589.1</v>
       </c>
       <c r="K37" s="9">
-        <v>0</v>
+        <v>818004.5</v>
       </c>
       <c r="L37" s="9">
-        <v>0</v>
+        <v>814116.3</v>
       </c>
       <c r="M37" s="9">
-        <v>0</v>
+        <v>844421.1</v>
       </c>
       <c r="N37" s="9">
-        <v>0</v>
+        <v>841581.4</v>
       </c>
       <c r="O37" s="9">
         <v>0</v>
       </c>
       <c r="P37" s="6"/>
       <c r="Q37" s="7">
-        <v>3198089.1999999997</v>
+        <v>8861577.6999999993</v>
       </c>
     </row>
     <row r="38" spans="2:17" x14ac:dyDescent="0.25">
@@ -5277,44 +5277,44 @@
       </c>
       <c r="C38" s="14"/>
       <c r="D38" s="11">
-        <v>1736734.2</v>
+        <v>1736819.9</v>
       </c>
       <c r="E38" s="11">
-        <v>1547634.2999999998</v>
+        <v>1550058.2</v>
       </c>
       <c r="F38" s="11">
-        <v>1721882</v>
+        <v>1723023.5999999999</v>
       </c>
       <c r="G38" s="11">
-        <v>1618262.5</v>
+        <v>1619586.5</v>
       </c>
       <c r="H38" s="11">
-        <v>0</v>
+        <v>1640078</v>
       </c>
       <c r="I38" s="11">
-        <v>0</v>
+        <v>1518150.6</v>
       </c>
       <c r="J38" s="11">
-        <v>0</v>
+        <v>1620137.7999999998</v>
       </c>
       <c r="K38" s="11">
-        <v>0</v>
+        <v>1628657.3</v>
       </c>
       <c r="L38" s="11">
-        <v>0</v>
+        <v>1601114.7000000002</v>
       </c>
       <c r="M38" s="11">
-        <v>0</v>
+        <v>1692877.9</v>
       </c>
       <c r="N38" s="11">
-        <v>0</v>
+        <v>1696550.9</v>
       </c>
       <c r="O38" s="11">
         <v>0</v>
       </c>
       <c r="P38" s="6"/>
       <c r="Q38" s="11">
-        <v>6624513</v>
+        <v>18027055.399999999</v>
       </c>
     </row>
     <row r="39" spans="2:17" x14ac:dyDescent="0.25">
@@ -5360,44 +5360,44 @@
       </c>
       <c r="C41" s="13"/>
       <c r="D41" s="11">
-        <v>4129.2</v>
+        <v>4232.5</v>
       </c>
       <c r="E41" s="11">
-        <v>3309.2</v>
+        <v>3402.5</v>
       </c>
       <c r="F41" s="11">
-        <v>3668.3</v>
+        <v>3635.6</v>
       </c>
       <c r="G41" s="11">
-        <v>3345.6</v>
+        <v>3557.2</v>
       </c>
       <c r="H41" s="11">
-        <v>0</v>
+        <v>3982.6</v>
       </c>
       <c r="I41" s="11">
-        <v>0</v>
+        <v>3614.6</v>
       </c>
       <c r="J41" s="11">
-        <v>0</v>
+        <v>3639.2</v>
       </c>
       <c r="K41" s="11">
-        <v>0</v>
+        <v>3443.6</v>
       </c>
       <c r="L41" s="11">
-        <v>0</v>
+        <v>4169.1000000000004</v>
       </c>
       <c r="M41" s="11">
-        <v>0</v>
+        <v>3917.4</v>
       </c>
       <c r="N41" s="11">
-        <v>0</v>
+        <v>2939.9</v>
       </c>
       <c r="O41" s="11">
         <v>0</v>
       </c>
       <c r="P41" s="6"/>
       <c r="Q41" s="6">
-        <v>14452.300000000001</v>
+        <v>40534.199999999997</v>
       </c>
     </row>
     <row r="42" spans="2:17" x14ac:dyDescent="0.25">
@@ -5406,44 +5406,44 @@
       </c>
       <c r="C42" s="13"/>
       <c r="D42" s="11">
-        <v>180027.2</v>
+        <v>179969.7</v>
       </c>
       <c r="E42" s="11">
-        <v>163319.6</v>
+        <v>163246.20000000001</v>
       </c>
       <c r="F42" s="11">
-        <v>181560</v>
+        <v>181872.6</v>
       </c>
       <c r="G42" s="11">
-        <v>167682.79999999999</v>
+        <v>168131.1</v>
       </c>
       <c r="H42" s="11">
-        <v>0</v>
+        <v>170475.7</v>
       </c>
       <c r="I42" s="11">
-        <v>0</v>
+        <v>164455.79999999999</v>
       </c>
       <c r="J42" s="11">
-        <v>0</v>
+        <v>168798.4</v>
       </c>
       <c r="K42" s="11">
-        <v>0</v>
+        <v>163098.1</v>
       </c>
       <c r="L42" s="11">
-        <v>0</v>
+        <v>150855.79999999999</v>
       </c>
       <c r="M42" s="11">
-        <v>0</v>
+        <v>162873.29999999999</v>
       </c>
       <c r="N42" s="11">
-        <v>0</v>
+        <v>167297.4</v>
       </c>
       <c r="O42" s="11">
         <v>0</v>
       </c>
       <c r="P42" s="6"/>
       <c r="Q42" s="6">
-        <v>692589.60000000009</v>
+        <v>1841074.1</v>
       </c>
     </row>
     <row r="43" spans="2:17" x14ac:dyDescent="0.25">
@@ -5452,44 +5452,44 @@
       </c>
       <c r="C43" s="13"/>
       <c r="D43" s="11">
-        <v>932.3</v>
+        <v>900.3</v>
       </c>
       <c r="E43" s="11">
-        <v>851.3</v>
+        <v>830.6</v>
       </c>
       <c r="F43" s="11">
-        <v>980.4</v>
+        <v>915.8</v>
       </c>
       <c r="G43" s="11">
-        <v>937.1</v>
+        <v>871</v>
       </c>
       <c r="H43" s="11">
-        <v>0</v>
+        <v>884.6</v>
       </c>
       <c r="I43" s="11">
-        <v>0</v>
+        <v>868.1</v>
       </c>
       <c r="J43" s="11">
-        <v>0</v>
+        <v>879.5</v>
       </c>
       <c r="K43" s="11">
-        <v>0</v>
+        <v>864</v>
       </c>
       <c r="L43" s="11">
-        <v>0</v>
+        <v>802</v>
       </c>
       <c r="M43" s="11">
-        <v>0</v>
+        <v>939.8</v>
       </c>
       <c r="N43" s="11">
-        <v>0</v>
+        <v>889.2</v>
       </c>
       <c r="O43" s="11">
         <v>0</v>
       </c>
       <c r="P43" s="6"/>
       <c r="Q43" s="6">
-        <v>3701.1</v>
+        <v>9644.9000000000015</v>
       </c>
     </row>
     <row r="44" spans="2:17" x14ac:dyDescent="0.25">
@@ -5498,44 +5498,44 @@
       </c>
       <c r="C44" s="13"/>
       <c r="D44" s="11">
-        <v>309554</v>
+        <v>309760.2</v>
       </c>
       <c r="E44" s="11">
-        <v>298816.2</v>
+        <v>301396.8</v>
       </c>
       <c r="F44" s="11">
-        <v>343934.5</v>
+        <v>347355.7</v>
       </c>
       <c r="G44" s="11">
-        <v>321985.90000000002</v>
+        <v>322458.7</v>
       </c>
       <c r="H44" s="11">
-        <v>0</v>
+        <v>325466.2</v>
       </c>
       <c r="I44" s="65">
-        <v>0</v>
+        <v>318283.7</v>
       </c>
       <c r="J44" s="11">
-        <v>0</v>
+        <v>317625.7</v>
       </c>
       <c r="K44" s="11">
-        <v>0</v>
+        <v>336050.2</v>
       </c>
       <c r="L44" s="11">
-        <v>0</v>
+        <v>301987.59999999998</v>
       </c>
       <c r="M44" s="11">
-        <v>0</v>
+        <v>325929.5</v>
       </c>
       <c r="N44" s="11">
-        <v>0</v>
+        <v>334024.5</v>
       </c>
       <c r="O44" s="11">
         <v>0</v>
       </c>
       <c r="P44" s="6"/>
       <c r="Q44" s="6">
-        <v>1274290.6000000001</v>
+        <v>3540338.8000000003</v>
       </c>
     </row>
     <row r="45" spans="2:17" x14ac:dyDescent="0.25">
@@ -5556,32 +5556,32 @@
         <v>1733.7</v>
       </c>
       <c r="H45" s="9">
-        <v>0</v>
+        <v>1342</v>
       </c>
       <c r="I45" s="9">
-        <v>0</v>
+        <v>1169.0999999999999</v>
       </c>
       <c r="J45" s="9">
-        <v>0</v>
+        <v>1097.9000000000001</v>
       </c>
       <c r="K45" s="9">
-        <v>0</v>
+        <v>1011.9</v>
       </c>
       <c r="L45" s="9">
-        <v>0</v>
+        <v>1107.9000000000001</v>
       </c>
       <c r="M45" s="9">
-        <v>0</v>
+        <v>1548.3</v>
       </c>
       <c r="N45" s="9">
-        <v>0</v>
+        <v>2059.5</v>
       </c>
       <c r="O45" s="9">
         <v>0</v>
       </c>
       <c r="P45" s="6"/>
       <c r="Q45" s="7">
-        <v>8605.5</v>
+        <v>17942.099999999999</v>
       </c>
     </row>
     <row r="46" spans="2:17" x14ac:dyDescent="0.25">
@@ -5590,44 +5590,44 @@
       </c>
       <c r="C46" s="14"/>
       <c r="D46" s="11">
-        <v>497013.3</v>
+        <v>497233.3</v>
       </c>
       <c r="E46" s="11">
-        <v>468716.70000000007</v>
+        <v>471296.5</v>
       </c>
       <c r="F46" s="11">
-        <v>532224</v>
+        <v>535860.5</v>
       </c>
       <c r="G46" s="11">
-        <v>495685.10000000003</v>
+        <v>496751.7</v>
       </c>
       <c r="H46" s="11">
-        <v>0</v>
+        <v>502151.10000000003</v>
       </c>
       <c r="I46" s="11">
-        <v>0</v>
+        <v>488391.3</v>
       </c>
       <c r="J46" s="11">
-        <v>0</v>
+        <v>492040.70000000007</v>
       </c>
       <c r="K46" s="11">
-        <v>0</v>
+        <v>504467.80000000005</v>
       </c>
       <c r="L46" s="11">
-        <v>0</v>
+        <v>458922.4</v>
       </c>
       <c r="M46" s="11">
-        <v>0</v>
+        <v>495208.3</v>
       </c>
       <c r="N46" s="11">
-        <v>0</v>
+        <v>507210.5</v>
       </c>
       <c r="O46" s="11">
         <v>0</v>
       </c>
       <c r="P46" s="6"/>
       <c r="Q46" s="11">
-        <v>1993639.1</v>
+        <v>5449534.0999999996</v>
       </c>
     </row>
     <row r="47" spans="2:17" x14ac:dyDescent="0.25">
@@ -5651,32 +5651,32 @@
         <v>560422.40000000002</v>
       </c>
       <c r="H48" s="11">
-        <v>0</v>
+        <v>584174.69999999995</v>
       </c>
       <c r="I48" s="11">
-        <v>0</v>
+        <v>554598.1</v>
       </c>
       <c r="J48" s="11">
-        <v>0</v>
+        <v>550349.5</v>
       </c>
       <c r="K48" s="11">
-        <v>0</v>
+        <v>582174.30000000005</v>
       </c>
       <c r="L48" s="11">
-        <v>0</v>
+        <v>558697.19999999995</v>
       </c>
       <c r="M48" s="11">
-        <v>0</v>
+        <v>554102</v>
       </c>
       <c r="N48" s="11">
-        <v>0</v>
+        <v>564451.5</v>
       </c>
       <c r="O48" s="11">
         <v>0</v>
       </c>
       <c r="P48" s="6"/>
       <c r="Q48" s="63">
-        <v>560422.40000000002</v>
+        <v>564451.5</v>
       </c>
     </row>
     <row r="49" spans="2:17" x14ac:dyDescent="0.25">
@@ -5685,44 +5685,44 @@
       </c>
       <c r="C49" s="13"/>
       <c r="D49" s="11">
-        <v>-94853.6</v>
+        <v>-101444.5</v>
       </c>
       <c r="E49" s="11">
-        <v>-115127.4</v>
+        <v>-116029.3</v>
       </c>
       <c r="F49" s="11">
-        <v>-114147.6</v>
+        <v>-116727.1</v>
       </c>
       <c r="G49" s="11">
-        <v>-84432.8</v>
+        <v>-85742.9</v>
       </c>
       <c r="H49" s="11">
-        <v>0</v>
+        <v>-98528.6</v>
       </c>
       <c r="I49" s="11">
-        <v>0</v>
+        <v>-103353.4</v>
       </c>
       <c r="J49" s="11">
-        <v>0</v>
+        <v>-115364.9</v>
       </c>
       <c r="K49" s="11">
-        <v>0</v>
+        <v>-113025.9</v>
       </c>
       <c r="L49" s="11">
-        <v>0</v>
+        <v>-117364.3</v>
       </c>
       <c r="M49" s="11">
-        <v>0</v>
+        <v>-120127.6</v>
       </c>
       <c r="N49" s="11">
-        <v>0</v>
+        <v>-118613.6</v>
       </c>
       <c r="O49" s="11">
         <v>0</v>
       </c>
       <c r="P49" s="6"/>
       <c r="Q49" s="6">
-        <v>-408561.39999999997</v>
+        <v>-1206322.1000000003</v>
       </c>
     </row>
     <row r="50" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -5747,44 +5747,44 @@
         <v>200</v>
       </c>
       <c r="D51" s="11">
-        <v>17024939.199999996</v>
+        <v>17013506.299999997</v>
       </c>
       <c r="E51" s="11">
-        <v>15657965.999999998</v>
+        <v>15654379.699999999</v>
       </c>
       <c r="F51" s="11">
-        <v>16094480.699999999</v>
+        <v>16084400</v>
       </c>
       <c r="G51" s="11">
-        <v>14144024.699999999</v>
+        <v>14141811.800000001</v>
       </c>
       <c r="H51" s="11">
-        <v>0</v>
+        <v>13702322.699999999</v>
       </c>
       <c r="I51" s="11">
-        <v>0</v>
+        <v>13479632.199999997</v>
       </c>
       <c r="J51" s="11">
-        <v>0</v>
+        <v>14003902.799999999</v>
       </c>
       <c r="K51" s="11">
-        <v>0</v>
+        <v>13723239.999999998</v>
       </c>
       <c r="L51" s="11">
-        <v>0</v>
+        <v>12917857.800000003</v>
       </c>
       <c r="M51" s="11">
-        <v>0</v>
+        <v>14448741.699999999</v>
       </c>
       <c r="N51" s="11">
-        <v>0</v>
+        <v>15443151.300000001</v>
       </c>
       <c r="O51" s="11">
         <v>0</v>
       </c>
       <c r="P51" s="6"/>
       <c r="Q51" s="6">
-        <v>62921410.599999994</v>
+        <v>160612946.30000001</v>
       </c>
     </row>
     <row r="52" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -5907,35 +5907,35 @@
         <v>545521.30000000005</v>
       </c>
       <c r="G56" s="11">
-        <v>331845.90000000002</v>
+        <v>331794.8</v>
       </c>
       <c r="H56" s="11">
-        <v>0</v>
+        <v>178977.4</v>
       </c>
       <c r="I56" s="11">
-        <v>0</v>
+        <v>122298.1</v>
       </c>
       <c r="J56" s="11">
-        <v>0</v>
+        <v>108120.5</v>
       </c>
       <c r="K56" s="11">
-        <v>0</v>
+        <v>100235.6</v>
       </c>
       <c r="L56" s="11">
-        <v>0</v>
+        <v>112555.1</v>
       </c>
       <c r="M56" s="11">
-        <v>0</v>
+        <v>316318.7</v>
       </c>
       <c r="N56" s="11">
-        <v>0</v>
+        <v>511516.5</v>
       </c>
       <c r="O56" s="11">
         <v>0</v>
       </c>
       <c r="P56" s="6"/>
       <c r="Q56" s="6">
-        <v>2348946.8000000003</v>
+        <v>3798917.6000000006</v>
       </c>
     </row>
     <row r="57" spans="2:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5947,41 +5947,41 @@
         <v>491297.1</v>
       </c>
       <c r="E57" s="11">
-        <v>552087.9</v>
+        <v>551433.30000000005</v>
       </c>
       <c r="F57" s="11">
         <v>408682.2</v>
       </c>
       <c r="G57" s="11">
-        <v>250234.7</v>
+        <v>250160.1</v>
       </c>
       <c r="H57" s="11">
-        <v>0</v>
+        <v>171950.1</v>
       </c>
       <c r="I57" s="11">
-        <v>0</v>
+        <v>102077.7</v>
       </c>
       <c r="J57" s="11">
-        <v>0</v>
+        <v>95729.8</v>
       </c>
       <c r="K57" s="11">
-        <v>0</v>
+        <v>79375.399999999994</v>
       </c>
       <c r="L57" s="11">
-        <v>0</v>
+        <v>117466.4</v>
       </c>
       <c r="M57" s="11">
-        <v>0</v>
+        <v>250068.6</v>
       </c>
       <c r="N57" s="11">
-        <v>0</v>
+        <v>350411.9</v>
       </c>
       <c r="O57" s="11">
         <v>0</v>
       </c>
       <c r="P57" s="6"/>
       <c r="Q57" s="6">
-        <v>1702301.9</v>
+        <v>2868652.6</v>
       </c>
     </row>
     <row r="58" spans="2:17" x14ac:dyDescent="0.25">
@@ -5999,35 +5999,35 @@
         <v>1298057.6000000001</v>
       </c>
       <c r="G58" s="11">
-        <v>1065127.2</v>
+        <v>1065115.6000000001</v>
       </c>
       <c r="H58" s="11">
-        <v>0</v>
+        <v>1063284.6000000001</v>
       </c>
       <c r="I58" s="11">
-        <v>0</v>
+        <v>1158831</v>
       </c>
       <c r="J58" s="11">
-        <v>0</v>
+        <v>1231127.8</v>
       </c>
       <c r="K58" s="11">
-        <v>0</v>
+        <v>1185823.8</v>
       </c>
       <c r="L58" s="11">
-        <v>0</v>
+        <v>1139079.5</v>
       </c>
       <c r="M58" s="11">
-        <v>0</v>
+        <v>1175827</v>
       </c>
       <c r="N58" s="11">
-        <v>0</v>
+        <v>1199049.5</v>
       </c>
       <c r="O58" s="11">
         <v>0</v>
       </c>
       <c r="P58" s="6"/>
       <c r="Q58" s="6">
-        <v>4923897.0999999996</v>
+        <v>13076908.699999999</v>
       </c>
     </row>
     <row r="59" spans="2:17" x14ac:dyDescent="0.25">
@@ -6054,44 +6054,44 @@
       </c>
       <c r="C60" s="13"/>
       <c r="D60" s="11">
-        <v>12158.5</v>
+        <v>11727.7</v>
       </c>
       <c r="E60" s="11">
-        <v>15144.9</v>
+        <v>15245.1</v>
       </c>
       <c r="F60" s="11">
-        <v>12320.6</v>
+        <v>12552.4</v>
       </c>
       <c r="G60" s="11">
-        <v>9826.5</v>
+        <v>10157</v>
       </c>
       <c r="H60" s="11">
-        <v>0</v>
+        <v>8358.7999999999993</v>
       </c>
       <c r="I60" s="11">
-        <v>0</v>
+        <v>8991.7000000000007</v>
       </c>
       <c r="J60" s="11">
-        <v>0</v>
+        <v>10338.4</v>
       </c>
       <c r="K60" s="11">
-        <v>0</v>
+        <v>10734.7</v>
       </c>
       <c r="L60" s="11">
-        <v>0</v>
+        <v>3810.2</v>
       </c>
       <c r="M60" s="11">
-        <v>0</v>
+        <v>6915.6</v>
       </c>
       <c r="N60" s="11">
-        <v>0</v>
+        <v>8890.7000000000007</v>
       </c>
       <c r="O60" s="11">
         <v>0</v>
       </c>
       <c r="P60" s="6"/>
       <c r="Q60" s="6">
-        <v>49450.5</v>
+        <v>107722.29999999999</v>
       </c>
     </row>
     <row r="61" spans="2:17" x14ac:dyDescent="0.25">
@@ -6112,32 +6112,32 @@
         <v>230397.4</v>
       </c>
       <c r="H61" s="11">
-        <v>0</v>
+        <v>243945.2</v>
       </c>
       <c r="I61" s="11">
-        <v>0</v>
+        <v>200843.2</v>
       </c>
       <c r="J61" s="11">
-        <v>0</v>
+        <v>240283.3</v>
       </c>
       <c r="K61" s="11">
-        <v>0</v>
+        <v>209646.7</v>
       </c>
       <c r="L61" s="11">
-        <v>0</v>
+        <v>176973.6</v>
       </c>
       <c r="M61" s="11">
-        <v>0</v>
+        <v>224123</v>
       </c>
       <c r="N61" s="11">
-        <v>0</v>
+        <v>262471.2</v>
       </c>
       <c r="O61" s="11">
         <v>0</v>
       </c>
       <c r="P61" s="6"/>
       <c r="Q61" s="6">
-        <v>971064.50000000012</v>
+        <v>2529350.7000000002</v>
       </c>
     </row>
     <row r="62" spans="2:17" x14ac:dyDescent="0.25">
@@ -6187,7 +6187,7 @@
         <v>75047.600000000006</v>
       </c>
       <c r="E64" s="11">
-        <v>69389.899999999994</v>
+        <v>69395.5</v>
       </c>
       <c r="F64" s="11">
         <v>96493.5</v>
@@ -6196,32 +6196,32 @@
         <v>86541.1</v>
       </c>
       <c r="H64" s="11">
-        <v>0</v>
+        <v>100528.8</v>
       </c>
       <c r="I64" s="11">
-        <v>0</v>
+        <v>125924.2</v>
       </c>
       <c r="J64" s="11">
-        <v>0</v>
+        <v>124552</v>
       </c>
       <c r="K64" s="11">
-        <v>0</v>
+        <v>124749.3</v>
       </c>
       <c r="L64" s="11">
-        <v>0</v>
+        <v>119266.9</v>
       </c>
       <c r="M64" s="11">
-        <v>0</v>
+        <v>120546</v>
       </c>
       <c r="N64" s="11">
-        <v>0</v>
+        <v>86521.8</v>
       </c>
       <c r="O64" s="11">
         <v>0</v>
       </c>
       <c r="P64" s="6"/>
       <c r="Q64" s="6">
-        <v>327472.09999999998</v>
+        <v>1129566.7</v>
       </c>
     </row>
     <row r="65" spans="2:17" x14ac:dyDescent="0.25">
@@ -6242,7 +6242,7 @@
         <v>179</v>
       </c>
       <c r="H65" s="11">
-        <v>0</v>
+        <v>313.39999999999998</v>
       </c>
       <c r="I65" s="11">
         <v>0</v>
@@ -6267,7 +6267,7 @@
       </c>
       <c r="P65" s="6"/>
       <c r="Q65" s="6">
-        <v>2035.1</v>
+        <v>2348.5</v>
       </c>
     </row>
     <row r="66" spans="2:17" x14ac:dyDescent="0.25">
@@ -6288,32 +6288,32 @@
         <v>46083.4</v>
       </c>
       <c r="H66" s="11">
-        <v>0</v>
+        <v>50369.599999999999</v>
       </c>
       <c r="I66" s="11">
-        <v>0</v>
+        <v>46053.9</v>
       </c>
       <c r="J66" s="11">
-        <v>0</v>
+        <v>51513.4</v>
       </c>
       <c r="K66" s="11">
-        <v>0</v>
+        <v>50084.9</v>
       </c>
       <c r="L66" s="11">
-        <v>0</v>
+        <v>43704.1</v>
       </c>
       <c r="M66" s="11">
-        <v>0</v>
+        <v>47784.2</v>
       </c>
       <c r="N66" s="11">
-        <v>0</v>
+        <v>45059.1</v>
       </c>
       <c r="O66" s="11">
         <v>0</v>
       </c>
       <c r="P66" s="6"/>
       <c r="Q66" s="6">
-        <v>192791.9</v>
+        <v>527361.10000000009</v>
       </c>
     </row>
     <row r="67" spans="2:17" x14ac:dyDescent="0.25">
@@ -6322,44 +6322,44 @@
       </c>
       <c r="C67" s="13"/>
       <c r="D67" s="9">
-        <v>259983.6</v>
+        <v>260009.7</v>
       </c>
       <c r="E67" s="9">
-        <v>238238.1</v>
+        <v>237311.6</v>
       </c>
       <c r="F67" s="9">
-        <v>274520</v>
+        <v>270775</v>
       </c>
       <c r="G67" s="9">
-        <v>238031.8</v>
+        <v>236868.3</v>
       </c>
       <c r="H67" s="9">
-        <v>0</v>
+        <v>208446</v>
       </c>
       <c r="I67" s="9">
-        <v>0</v>
+        <v>215926.6</v>
       </c>
       <c r="J67" s="9">
-        <v>0</v>
+        <v>201170.2</v>
       </c>
       <c r="K67" s="9">
-        <v>0</v>
+        <v>206830.4</v>
       </c>
       <c r="L67" s="9">
-        <v>0</v>
+        <v>253292.9</v>
       </c>
       <c r="M67" s="9">
-        <v>0</v>
+        <v>245001.7</v>
       </c>
       <c r="N67" s="9">
-        <v>0</v>
+        <v>252749.1</v>
       </c>
       <c r="O67" s="9">
         <v>0</v>
       </c>
       <c r="P67" s="6"/>
       <c r="Q67" s="7">
-        <v>1010773.5</v>
+        <v>2588381.5</v>
       </c>
     </row>
     <row r="68" spans="2:17" x14ac:dyDescent="0.25">
@@ -6368,44 +6368,44 @@
       </c>
       <c r="C68" s="13"/>
       <c r="D68" s="11">
-        <v>386700.79999999999</v>
+        <v>386726.9</v>
       </c>
       <c r="E68" s="11">
-        <v>353538.4</v>
+        <v>352617.5</v>
       </c>
       <c r="F68" s="11">
-        <v>421998.1</v>
+        <v>418253.1</v>
       </c>
       <c r="G68" s="11">
-        <v>370835.3</v>
+        <v>369671.8</v>
       </c>
       <c r="H68" s="11">
-        <v>0</v>
+        <v>359657.8</v>
       </c>
       <c r="I68" s="11">
-        <v>0</v>
+        <v>387904.7</v>
       </c>
       <c r="J68" s="11">
-        <v>0</v>
+        <v>377235.6</v>
       </c>
       <c r="K68" s="11">
-        <v>0</v>
+        <v>381664.6</v>
       </c>
       <c r="L68" s="11">
-        <v>0</v>
+        <v>416263.9</v>
       </c>
       <c r="M68" s="11">
-        <v>0</v>
+        <v>413331.9</v>
       </c>
       <c r="N68" s="11">
-        <v>0</v>
+        <v>384330</v>
       </c>
       <c r="O68" s="11">
         <v>0</v>
       </c>
       <c r="P68" s="6"/>
       <c r="Q68" s="11">
-        <v>1533072.6</v>
+        <v>4247657.8</v>
       </c>
     </row>
     <row r="69" spans="2:17" x14ac:dyDescent="0.25">
@@ -6452,44 +6452,44 @@
       </c>
       <c r="C71" s="13"/>
       <c r="D71" s="11">
-        <v>294362.3</v>
+        <v>298214.5</v>
       </c>
       <c r="E71" s="11">
-        <v>237831.2</v>
+        <v>238894.4</v>
       </c>
       <c r="F71" s="11">
-        <v>306979</v>
+        <v>309003.2</v>
       </c>
       <c r="G71" s="11">
-        <v>266593.59999999998</v>
+        <v>268487.8</v>
       </c>
       <c r="H71" s="11">
-        <v>0</v>
+        <v>249748.1</v>
       </c>
       <c r="I71" s="11">
-        <v>0</v>
+        <v>240323.4</v>
       </c>
       <c r="J71" s="11">
-        <v>0</v>
+        <v>307791</v>
       </c>
       <c r="K71" s="11">
-        <v>0</v>
+        <v>286317.90000000002</v>
       </c>
       <c r="L71" s="11">
-        <v>0</v>
+        <v>256238.2</v>
       </c>
       <c r="M71" s="11">
-        <v>0</v>
+        <v>280520.8</v>
       </c>
       <c r="N71" s="11">
-        <v>0</v>
+        <v>281042.59999999998</v>
       </c>
       <c r="O71" s="11">
         <v>0</v>
       </c>
       <c r="P71" s="6"/>
       <c r="Q71" s="6">
-        <v>1105766.1000000001</v>
+        <v>3016581.9000000004</v>
       </c>
     </row>
     <row r="72" spans="2:17" x14ac:dyDescent="0.25">
@@ -6507,35 +6507,35 @@
         <v>5656.3</v>
       </c>
       <c r="G72" s="11">
-        <v>7692.4</v>
+        <v>7688.9</v>
       </c>
       <c r="H72" s="11">
-        <v>0</v>
+        <v>5981.4</v>
       </c>
       <c r="I72" s="11">
-        <v>0</v>
+        <v>12883.2</v>
       </c>
       <c r="J72" s="11">
-        <v>0</v>
+        <v>5993.3</v>
       </c>
       <c r="K72" s="11">
-        <v>0</v>
+        <v>6449.7</v>
       </c>
       <c r="L72" s="11">
-        <v>0</v>
+        <v>5941.1</v>
       </c>
       <c r="M72" s="11">
-        <v>0</v>
+        <v>5632.6</v>
       </c>
       <c r="N72" s="11">
-        <v>0</v>
+        <v>6438.6</v>
       </c>
       <c r="O72" s="11">
         <v>0</v>
       </c>
       <c r="P72" s="6"/>
       <c r="Q72" s="6">
-        <v>24627.599999999999</v>
+        <v>73944</v>
       </c>
     </row>
     <row r="73" spans="2:17" x14ac:dyDescent="0.25">
@@ -6544,44 +6544,44 @@
       </c>
       <c r="C73" s="15"/>
       <c r="D73" s="11">
-        <v>1804706.5</v>
+        <v>1803058</v>
       </c>
       <c r="E73" s="11">
-        <v>1606224.1</v>
+        <v>1606896.1</v>
       </c>
       <c r="F73" s="11">
-        <v>1751567.4</v>
+        <v>1752119.7</v>
       </c>
       <c r="G73" s="11">
-        <v>1639470.7</v>
+        <v>1640141.3</v>
       </c>
       <c r="H73" s="11">
-        <v>0</v>
+        <v>1582741.5</v>
       </c>
       <c r="I73" s="11">
-        <v>0</v>
+        <v>1552375.9</v>
       </c>
       <c r="J73" s="11">
-        <v>0</v>
+        <v>1705621.3</v>
       </c>
       <c r="K73" s="11">
-        <v>0</v>
+        <v>1756067.6</v>
       </c>
       <c r="L73" s="11">
-        <v>0</v>
+        <v>1596965.7</v>
       </c>
       <c r="M73" s="11">
-        <v>0</v>
+        <v>1704595.3</v>
       </c>
       <c r="N73" s="11">
-        <v>0</v>
+        <v>1755517.4</v>
       </c>
       <c r="O73" s="11">
         <v>0</v>
       </c>
       <c r="P73" s="6"/>
       <c r="Q73" s="6">
-        <v>6801968.7000000002</v>
+        <v>18456099.800000001</v>
       </c>
     </row>
     <row r="74" spans="2:17" x14ac:dyDescent="0.25">
@@ -6602,32 +6602,32 @@
         <v>182.6</v>
       </c>
       <c r="H74" s="9">
-        <v>0</v>
+        <v>238.9</v>
       </c>
       <c r="I74" s="9">
-        <v>0</v>
+        <v>92.1</v>
       </c>
       <c r="J74" s="9">
-        <v>0</v>
+        <v>165.4</v>
       </c>
       <c r="K74" s="9">
-        <v>0</v>
+        <v>100.2</v>
       </c>
       <c r="L74" s="9">
-        <v>0</v>
+        <v>84.6</v>
       </c>
       <c r="M74" s="9">
-        <v>0</v>
+        <v>57.3</v>
       </c>
       <c r="N74" s="9">
-        <v>0</v>
+        <v>80.900000000000006</v>
       </c>
       <c r="O74" s="9">
         <v>0</v>
       </c>
       <c r="P74" s="6"/>
       <c r="Q74" s="7">
-        <v>446</v>
+        <v>1265.3999999999999</v>
       </c>
     </row>
     <row r="75" spans="2:17" x14ac:dyDescent="0.25">
@@ -6636,44 +6636,44 @@
       </c>
       <c r="C75" s="13"/>
       <c r="D75" s="11">
-        <v>2105013</v>
+        <v>2107216.6999999997</v>
       </c>
       <c r="E75" s="11">
-        <v>1849563.2000000002</v>
+        <v>1851298.4000000001</v>
       </c>
       <c r="F75" s="11">
-        <v>2064292.9</v>
+        <v>2066869.4</v>
       </c>
       <c r="G75" s="11">
-        <v>1913939.3</v>
+        <v>1916500.6</v>
       </c>
       <c r="H75" s="11">
-        <v>0</v>
+        <v>1838709.9</v>
       </c>
       <c r="I75" s="11">
-        <v>0</v>
+        <v>1805674.6</v>
       </c>
       <c r="J75" s="11">
-        <v>0</v>
+        <v>2019571</v>
       </c>
       <c r="K75" s="11">
-        <v>0</v>
+        <v>2048935.4000000001</v>
       </c>
       <c r="L75" s="11">
-        <v>0</v>
+        <v>1859229.6</v>
       </c>
       <c r="M75" s="11">
-        <v>0</v>
+        <v>1990806</v>
       </c>
       <c r="N75" s="11">
-        <v>0</v>
+        <v>2043079.4999999998</v>
       </c>
       <c r="O75" s="11">
         <v>0</v>
       </c>
       <c r="P75" s="6"/>
       <c r="Q75" s="11">
-        <v>7932808.4000000004</v>
+        <v>21547891.100000001</v>
       </c>
     </row>
     <row r="76" spans="2:17" x14ac:dyDescent="0.25">
@@ -6726,38 +6726,38 @@
         <v>32567.3</v>
       </c>
       <c r="F78" s="11">
-        <v>37004.699999999997</v>
+        <v>37004.199999999997</v>
       </c>
       <c r="G78" s="11">
         <v>52972.2</v>
       </c>
       <c r="H78" s="11">
-        <v>0</v>
+        <v>95665.7</v>
       </c>
       <c r="I78" s="11">
-        <v>0</v>
+        <v>97567.4</v>
       </c>
       <c r="J78" s="11">
-        <v>0</v>
+        <v>60657.3</v>
       </c>
       <c r="K78" s="11">
-        <v>0</v>
+        <v>60170.8</v>
       </c>
       <c r="L78" s="11">
-        <v>0</v>
+        <v>72600.399999999994</v>
       </c>
       <c r="M78" s="11">
-        <v>0</v>
+        <v>62612.800000000003</v>
       </c>
       <c r="N78" s="11">
-        <v>0</v>
+        <v>48888.4</v>
       </c>
       <c r="O78" s="11">
         <v>0</v>
       </c>
       <c r="P78" s="6"/>
       <c r="Q78" s="6">
-        <v>169347.7</v>
+        <v>667510.00000000012</v>
       </c>
     </row>
     <row r="79" spans="2:17" x14ac:dyDescent="0.25">
@@ -6766,44 +6766,44 @@
       </c>
       <c r="C79" s="15"/>
       <c r="D79" s="11">
-        <v>1035404.5</v>
+        <v>1035471.7</v>
       </c>
       <c r="E79" s="11">
-        <v>931943.8</v>
+        <v>931850.4</v>
       </c>
       <c r="F79" s="11">
-        <v>1015053.3</v>
+        <v>1014706.8</v>
       </c>
       <c r="G79" s="11">
-        <v>866767.3</v>
+        <v>866620.8</v>
       </c>
       <c r="H79" s="11">
-        <v>0</v>
+        <v>680117.5</v>
       </c>
       <c r="I79" s="11">
-        <v>0</v>
+        <v>799089.1</v>
       </c>
       <c r="J79" s="11">
-        <v>0</v>
+        <v>850065.1</v>
       </c>
       <c r="K79" s="11">
-        <v>0</v>
+        <v>866048.7</v>
       </c>
       <c r="L79" s="11">
-        <v>0</v>
+        <v>794894.6</v>
       </c>
       <c r="M79" s="11">
-        <v>0</v>
+        <v>906484.3</v>
       </c>
       <c r="N79" s="11">
-        <v>0</v>
+        <v>964129.5</v>
       </c>
       <c r="O79" s="11">
         <v>0</v>
       </c>
       <c r="P79" s="6"/>
       <c r="Q79" s="6">
-        <v>3849168.9000000004</v>
+        <v>9709478.5</v>
       </c>
     </row>
     <row r="80" spans="2:17" x14ac:dyDescent="0.25">
@@ -6824,32 +6824,32 @@
         <v>55448.4</v>
       </c>
       <c r="H80" s="9">
-        <v>0</v>
+        <v>82002.2</v>
       </c>
       <c r="I80" s="9">
-        <v>0</v>
+        <v>69979.600000000006</v>
       </c>
       <c r="J80" s="9">
-        <v>0</v>
+        <v>66291.7</v>
       </c>
       <c r="K80" s="9">
-        <v>0</v>
+        <v>71652.600000000006</v>
       </c>
       <c r="L80" s="9">
-        <v>0</v>
+        <v>65934.600000000006</v>
       </c>
       <c r="M80" s="9">
-        <v>0</v>
+        <v>72994.5</v>
       </c>
       <c r="N80" s="9">
-        <v>0</v>
+        <v>77801.2</v>
       </c>
       <c r="O80" s="9">
         <v>0</v>
       </c>
       <c r="P80" s="6"/>
       <c r="Q80" s="7">
-        <v>295587.5</v>
+        <v>802243.9</v>
       </c>
     </row>
     <row r="81" spans="2:17" x14ac:dyDescent="0.25">
@@ -6858,44 +6858,44 @@
       </c>
       <c r="C81" s="13"/>
       <c r="D81" s="23">
-        <v>1163807.7</v>
+        <v>1163874.8999999999</v>
       </c>
       <c r="E81" s="23">
-        <v>1041177.6000000001</v>
+        <v>1041084.2000000001</v>
       </c>
       <c r="F81" s="23">
-        <v>1133930.8999999999</v>
+        <v>1133583.8999999999</v>
       </c>
       <c r="G81" s="23">
-        <v>975187.9</v>
+        <v>975041.4</v>
       </c>
       <c r="H81" s="23">
-        <v>0</v>
+        <v>857785.39999999991</v>
       </c>
       <c r="I81" s="23">
-        <v>0</v>
+        <v>966636.1</v>
       </c>
       <c r="J81" s="23">
-        <v>0</v>
+        <v>977014.1</v>
       </c>
       <c r="K81" s="23">
-        <v>0</v>
+        <v>997872.1</v>
       </c>
       <c r="L81" s="23">
-        <v>0</v>
+        <v>933429.6</v>
       </c>
       <c r="M81" s="23">
-        <v>0</v>
+        <v>1042091.6000000001</v>
       </c>
       <c r="N81" s="23">
-        <v>0</v>
+        <v>1090819.1000000001</v>
       </c>
       <c r="O81" s="23">
         <v>0</v>
       </c>
       <c r="P81" s="6"/>
       <c r="Q81" s="23">
-        <v>4314104.1000000006</v>
+        <v>11179232.4</v>
       </c>
     </row>
     <row r="82" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -6922,44 +6922,44 @@
       </c>
       <c r="C83" s="14"/>
       <c r="D83" s="11">
-        <v>6430446.1000000006</v>
+        <v>6432312.3000000007</v>
       </c>
       <c r="E83" s="11">
-        <v>6067507.1999999993</v>
+        <v>6067673.7000000011</v>
       </c>
       <c r="F83" s="11">
-        <v>6130298.4000000004</v>
+        <v>6129014.6999999993</v>
       </c>
       <c r="G83" s="11">
-        <v>5147394.2</v>
+        <v>5148838.7</v>
       </c>
       <c r="H83" s="11">
-        <v>0</v>
+        <v>4722669.1999999993</v>
       </c>
       <c r="I83" s="11">
-        <v>0</v>
+        <v>4753257.0999999996</v>
       </c>
       <c r="J83" s="11">
-        <v>0</v>
+        <v>5059420.5</v>
       </c>
       <c r="K83" s="11">
-        <v>0</v>
+        <v>5014288.3</v>
       </c>
       <c r="L83" s="11">
-        <v>0</v>
+        <v>4758807.9000000004</v>
       </c>
       <c r="M83" s="11">
-        <v>0</v>
+        <v>5419482.4000000004</v>
       </c>
       <c r="N83" s="11">
-        <v>0</v>
+        <v>5850568.4000000004</v>
       </c>
       <c r="O83" s="11">
         <v>0</v>
       </c>
       <c r="P83" s="6"/>
       <c r="Q83" s="11">
-        <v>23775645.900000002</v>
+        <v>59356333.199999996</v>
       </c>
     </row>
     <row r="84" spans="2:17" x14ac:dyDescent="0.25">
@@ -7014,35 +7014,35 @@
         <v>909875.07</v>
       </c>
       <c r="G86" s="11">
-        <v>1025040.03</v>
+        <v>749719.26</v>
       </c>
       <c r="H86" s="11">
-        <v>0</v>
+        <v>710654.77</v>
       </c>
       <c r="I86" s="11">
-        <v>0</v>
+        <v>731089.66</v>
       </c>
       <c r="J86" s="11">
-        <v>0</v>
+        <v>683803.37</v>
       </c>
       <c r="K86" s="11">
-        <v>0</v>
+        <v>728447.49</v>
       </c>
       <c r="L86" s="11">
-        <v>0</v>
+        <v>662679.05000000005</v>
       </c>
       <c r="M86" s="65">
-        <v>0</v>
+        <v>722643.06</v>
       </c>
       <c r="N86" s="11">
-        <v>0</v>
+        <v>991467.4</v>
       </c>
       <c r="O86" s="11">
         <v>0</v>
       </c>
       <c r="P86" s="6"/>
       <c r="Q86" s="97">
-        <v>3739337.1799999997</v>
+        <v>8694801.2100000009</v>
       </c>
     </row>
     <row r="87" spans="2:17" x14ac:dyDescent="0.25">
@@ -7060,35 +7060,35 @@
         <v>1752518.07</v>
       </c>
       <c r="G87" s="11">
-        <v>2031525.17</v>
+        <v>1490541.11</v>
       </c>
       <c r="H87" s="11">
-        <v>0</v>
+        <v>1507213.09</v>
       </c>
       <c r="I87" s="11">
-        <v>0</v>
+        <v>1580214.66</v>
       </c>
       <c r="J87" s="11">
-        <v>0</v>
+        <v>1477679.08</v>
       </c>
       <c r="K87" s="11">
-        <v>0</v>
+        <v>1605591.39</v>
       </c>
       <c r="L87" s="11">
-        <v>0</v>
+        <v>1338132.56</v>
       </c>
       <c r="M87" s="65">
-        <v>0</v>
+        <v>1530956.03</v>
       </c>
       <c r="N87" s="11">
-        <v>0</v>
+        <v>2071075.56</v>
       </c>
       <c r="O87" s="11">
         <v>0</v>
       </c>
       <c r="P87" s="6"/>
       <c r="Q87" s="97">
-        <v>7352260.0200000005</v>
+        <v>17922138.330000002</v>
       </c>
     </row>
     <row r="88" spans="2:17" x14ac:dyDescent="0.25">
@@ -7106,35 +7106,35 @@
         <v>488706.05</v>
       </c>
       <c r="G88" s="11">
-        <v>521826.78</v>
+        <v>605425.02</v>
       </c>
       <c r="H88" s="11">
-        <v>0</v>
+        <v>548708.35</v>
       </c>
       <c r="I88" s="11">
-        <v>0</v>
+        <v>354535.56</v>
       </c>
       <c r="J88" s="11">
-        <v>0</v>
+        <v>469482.17</v>
       </c>
       <c r="K88" s="11">
-        <v>0</v>
+        <v>510303.58</v>
       </c>
       <c r="L88" s="11">
-        <v>0</v>
+        <v>421029.77</v>
       </c>
       <c r="M88" s="65">
-        <v>0</v>
+        <v>603717.19999999995</v>
       </c>
       <c r="N88" s="11">
-        <v>0</v>
+        <v>523351.19</v>
       </c>
       <c r="O88" s="11">
         <v>0</v>
       </c>
       <c r="P88" s="6"/>
       <c r="Q88" s="97">
-        <v>2203242.66</v>
+        <v>5717968.7200000007</v>
       </c>
     </row>
     <row r="89" spans="2:17" x14ac:dyDescent="0.25">
@@ -7152,35 +7152,35 @@
         <v>1438599.38</v>
       </c>
       <c r="G89" s="11">
-        <v>1468046.3</v>
+        <v>1329838</v>
       </c>
       <c r="H89" s="11">
-        <v>0</v>
+        <v>1316837.32</v>
       </c>
       <c r="I89" s="11">
-        <v>0</v>
+        <v>1128392.51</v>
       </c>
       <c r="J89" s="11">
-        <v>0</v>
+        <v>1286359.31</v>
       </c>
       <c r="K89" s="11">
-        <v>0</v>
+        <v>1275293.6200000001</v>
       </c>
       <c r="L89" s="11">
-        <v>0</v>
+        <v>1345306.55</v>
       </c>
       <c r="M89" s="65">
-        <v>0</v>
+        <v>1347203.64</v>
       </c>
       <c r="N89" s="11">
-        <v>0</v>
+        <v>1396256.37</v>
       </c>
       <c r="O89" s="11">
         <v>0</v>
       </c>
       <c r="P89" s="6"/>
       <c r="Q89" s="97">
-        <v>5445862.3300000001</v>
+        <v>14403303.350000001</v>
       </c>
     </row>
     <row r="90" spans="2:17" x14ac:dyDescent="0.25">
@@ -7198,35 +7198,35 @@
         <v>19726.45</v>
       </c>
       <c r="G90" s="11">
-        <v>16807.95</v>
+        <v>16303.39</v>
       </c>
       <c r="H90" s="11">
-        <v>0</v>
+        <v>14040.1</v>
       </c>
       <c r="I90" s="11">
-        <v>0</v>
+        <v>18616.7</v>
       </c>
       <c r="J90" s="11">
-        <v>0</v>
+        <v>31131.97</v>
       </c>
       <c r="K90" s="11">
-        <v>0</v>
+        <v>24918.02</v>
       </c>
       <c r="L90" s="11">
-        <v>0</v>
+        <v>17978.96</v>
       </c>
       <c r="M90" s="65">
-        <v>0</v>
+        <v>24487.55</v>
       </c>
       <c r="N90" s="11">
-        <v>0</v>
+        <v>9174.5</v>
       </c>
       <c r="O90" s="11">
         <v>0</v>
       </c>
       <c r="P90" s="6"/>
       <c r="Q90" s="97">
-        <v>89974</v>
+        <v>229817.24</v>
       </c>
     </row>
     <row r="91" spans="2:17" x14ac:dyDescent="0.25">
@@ -7336,35 +7336,35 @@
         <v>4609425.0200000005</v>
       </c>
       <c r="G93" s="11">
-        <v>5063246.2300000004</v>
+        <v>4191826.7800000003</v>
       </c>
       <c r="H93" s="11">
-        <v>0</v>
+        <v>4097453.6300000004</v>
       </c>
       <c r="I93" s="11">
-        <v>0</v>
+        <v>3812849.09</v>
       </c>
       <c r="J93" s="11">
-        <v>0</v>
+        <v>3948455.9000000004</v>
       </c>
       <c r="K93" s="11">
-        <v>0</v>
+        <v>4144554.1</v>
       </c>
       <c r="L93" s="11">
-        <v>0</v>
+        <v>3785126.8899999997</v>
       </c>
       <c r="M93" s="65">
-        <v>0</v>
+        <v>4229007.4799999995</v>
       </c>
       <c r="N93" s="11">
-        <v>0</v>
+        <v>4991325.0199999996</v>
       </c>
       <c r="O93" s="11">
         <v>0</v>
       </c>
       <c r="P93" s="6"/>
       <c r="Q93" s="65">
-        <v>18830676.189999998</v>
+        <v>46968028.850000009</v>
       </c>
     </row>
     <row r="94" spans="2:17" x14ac:dyDescent="0.25">
@@ -7420,35 +7420,35 @@
         <v>62863.76</v>
       </c>
       <c r="G96" s="11">
-        <v>50904.74</v>
+        <v>38590.47</v>
       </c>
       <c r="H96" s="11">
-        <v>0</v>
+        <v>40638.68</v>
       </c>
       <c r="I96" s="11">
-        <v>0</v>
+        <v>62878.84</v>
       </c>
       <c r="J96" s="11">
-        <v>0</v>
+        <v>63015.51</v>
       </c>
       <c r="K96" s="11">
-        <v>0</v>
+        <v>60840.91</v>
       </c>
       <c r="L96" s="11">
-        <v>0</v>
+        <v>51708.160000000003</v>
       </c>
       <c r="M96" s="65">
-        <v>0</v>
+        <v>55489.27</v>
       </c>
       <c r="N96" s="11">
-        <v>0</v>
+        <v>81485.399999999994</v>
       </c>
       <c r="O96" s="11">
         <v>0</v>
       </c>
       <c r="P96" s="6"/>
       <c r="Q96" s="97">
-        <v>201143.67</v>
+        <v>604886.17000000016</v>
       </c>
     </row>
     <row r="97" spans="2:17" x14ac:dyDescent="0.25">
@@ -7466,35 +7466,35 @@
         <v>2241920.7000000002</v>
       </c>
       <c r="G97" s="11">
-        <v>1238166.8999999999</v>
+        <v>2170061.8199999998</v>
       </c>
       <c r="H97" s="11">
-        <v>0</v>
+        <v>2136822.9300000002</v>
       </c>
       <c r="I97" s="11">
-        <v>0</v>
+        <v>1941660.15</v>
       </c>
       <c r="J97" s="11">
-        <v>0</v>
+        <v>2029079.13</v>
       </c>
       <c r="K97" s="11">
-        <v>0</v>
+        <v>2002065.18</v>
       </c>
       <c r="L97" s="11">
-        <v>0</v>
+        <v>2050190.77</v>
       </c>
       <c r="M97" s="65">
-        <v>0</v>
+        <v>2114519.87</v>
       </c>
       <c r="N97" s="11">
-        <v>0</v>
+        <v>1449408.53</v>
       </c>
       <c r="O97" s="11">
         <v>0</v>
       </c>
       <c r="P97" s="6"/>
       <c r="Q97" s="97">
-        <v>8309656.9399999995</v>
+        <v>22965298.420000002</v>
       </c>
     </row>
     <row r="98" spans="2:17" x14ac:dyDescent="0.25">
@@ -7512,35 +7512,35 @@
         <v>140770.10999999999</v>
       </c>
       <c r="G98" s="11">
-        <v>171232.91</v>
+        <v>120280.87</v>
       </c>
       <c r="H98" s="11">
-        <v>0</v>
+        <v>119626.96</v>
       </c>
       <c r="I98" s="11">
-        <v>0</v>
+        <v>105044.06</v>
       </c>
       <c r="J98" s="11">
-        <v>0</v>
+        <v>110310.06</v>
       </c>
       <c r="K98" s="11">
-        <v>0</v>
+        <v>115857.52</v>
       </c>
       <c r="L98" s="11">
-        <v>0</v>
+        <v>85101.92</v>
       </c>
       <c r="M98" s="65">
-        <v>0</v>
+        <v>116755.69</v>
       </c>
       <c r="N98" s="11">
-        <v>0</v>
+        <v>160654.91</v>
       </c>
       <c r="O98" s="11">
         <v>0</v>
       </c>
       <c r="P98" s="6"/>
       <c r="Q98" s="97">
-        <v>576425.78</v>
+        <v>1338824.8599999999</v>
       </c>
     </row>
     <row r="99" spans="2:17" x14ac:dyDescent="0.25">
@@ -7558,35 +7558,35 @@
         <v>268488.07</v>
       </c>
       <c r="G99" s="11">
-        <v>368205.95</v>
+        <v>358745.57</v>
       </c>
       <c r="H99" s="11">
-        <v>0</v>
+        <v>416130.94</v>
       </c>
       <c r="I99" s="11">
-        <v>0</v>
+        <v>310010.39</v>
       </c>
       <c r="J99" s="11">
-        <v>0</v>
+        <v>444587.45</v>
       </c>
       <c r="K99" s="11">
-        <v>0</v>
+        <v>445360.08</v>
       </c>
       <c r="L99" s="11">
-        <v>0</v>
+        <v>355606.32</v>
       </c>
       <c r="M99" s="65">
-        <v>0</v>
+        <v>363041.82</v>
       </c>
       <c r="N99" s="11">
-        <v>0</v>
+        <v>337124.29</v>
       </c>
       <c r="O99" s="11">
         <v>0</v>
       </c>
       <c r="P99" s="6"/>
       <c r="Q99" s="97">
-        <v>1344084.43</v>
+        <v>4006485.34</v>
       </c>
     </row>
     <row r="100" spans="2:17" x14ac:dyDescent="0.25">
@@ -7604,35 +7604,35 @@
         <v>1180774.94</v>
       </c>
       <c r="G100" s="9">
-        <v>1020633.3</v>
+        <v>1032884.5</v>
       </c>
       <c r="H100" s="9">
-        <v>0</v>
+        <v>1058878.94</v>
       </c>
       <c r="I100" s="9">
-        <v>0</v>
+        <v>1108285.31</v>
       </c>
       <c r="J100" s="9">
-        <v>0</v>
+        <v>1187756.6599999999</v>
       </c>
       <c r="K100" s="9">
-        <v>0</v>
+        <v>1020661.44</v>
       </c>
       <c r="L100" s="9">
-        <v>0</v>
+        <v>1156549.79</v>
       </c>
       <c r="M100" s="64">
-        <v>0</v>
+        <v>1075399.74</v>
       </c>
       <c r="N100" s="9">
-        <v>0</v>
+        <v>1101652.19</v>
       </c>
       <c r="O100" s="9">
         <v>0</v>
       </c>
       <c r="P100" s="6"/>
       <c r="Q100" s="98">
-        <v>4575401.5</v>
+        <v>12296836.77</v>
       </c>
     </row>
     <row r="101" spans="2:17" x14ac:dyDescent="0.25">
@@ -7650,35 +7650,35 @@
         <v>3894817.5799999996</v>
       </c>
       <c r="G101" s="23">
-        <v>2849143.8</v>
+        <v>3720563.23</v>
       </c>
       <c r="H101" s="23">
-        <v>0</v>
+        <v>3772098.45</v>
       </c>
       <c r="I101" s="23">
-        <v>0</v>
+        <v>3527878.75</v>
       </c>
       <c r="J101" s="23">
-        <v>0</v>
+        <v>3834748.8099999996</v>
       </c>
       <c r="K101" s="23">
-        <v>0</v>
+        <v>3644785.13</v>
       </c>
       <c r="L101" s="23">
-        <v>0</v>
+        <v>3699156.96</v>
       </c>
       <c r="M101" s="94">
-        <v>0</v>
+        <v>3725206.3899999997</v>
       </c>
       <c r="N101" s="23">
-        <v>0</v>
+        <v>3130325.32</v>
       </c>
       <c r="O101" s="23">
         <v>0</v>
       </c>
       <c r="P101" s="6"/>
       <c r="Q101" s="94">
-        <v>15006712.32</v>
+        <v>41212331.559999995</v>
       </c>
     </row>
     <row r="102" spans="2:17" x14ac:dyDescent="0.25">
@@ -7844,35 +7844,35 @@
         <v>8504242.5999999996</v>
       </c>
       <c r="G107" s="11">
-        <v>7912390.0300000003</v>
+        <v>7912390.0099999998</v>
       </c>
       <c r="H107" s="11">
-        <v>0</v>
+        <v>7869552.0800000001</v>
       </c>
       <c r="I107" s="11">
-        <v>0</v>
+        <v>7340727.8399999999</v>
       </c>
       <c r="J107" s="11">
-        <v>0</v>
+        <v>7783204.71</v>
       </c>
       <c r="K107" s="11">
-        <v>0</v>
+        <v>7789339.2300000004</v>
       </c>
       <c r="L107" s="11">
-        <v>0</v>
+        <v>7484283.8499999996</v>
       </c>
       <c r="M107" s="65">
-        <v>0</v>
+        <v>7954213.8699999992</v>
       </c>
       <c r="N107" s="11">
-        <v>0</v>
+        <v>8121650.3399999999</v>
       </c>
       <c r="O107" s="11">
         <v>0</v>
       </c>
       <c r="P107" s="6"/>
       <c r="Q107" s="97">
-        <v>33837388.509999998</v>
+        <v>88180360.409999996</v>
       </c>
     </row>
     <row r="108" spans="2:17" x14ac:dyDescent="0.25">
@@ -7889,34 +7889,34 @@
         <v>274330.40645161289</v>
       </c>
       <c r="G108" s="11">
-        <v>263746.33433333336</v>
+        <v>263746.33366666664</v>
       </c>
       <c r="H108" s="11">
-        <v>0</v>
+        <v>253856.51870967742</v>
       </c>
       <c r="I108" s="11">
-        <v>0</v>
+        <v>244690.92799999999</v>
       </c>
       <c r="J108" s="11">
-        <v>0</v>
+        <v>251071.11967741937</v>
       </c>
       <c r="K108" s="11">
-        <v>0</v>
+        <v>251269.00741935486</v>
       </c>
       <c r="L108" s="11">
-        <v>0</v>
+        <v>249476.12833333333</v>
       </c>
       <c r="M108" s="65">
-        <v>0</v>
+        <v>256587.54419354835</v>
       </c>
       <c r="N108" s="11">
-        <v>0</v>
+        <v>270721.67800000001</v>
       </c>
       <c r="O108" s="11">
         <v>0</v>
       </c>
       <c r="Q108" s="99">
-        <v>282351.50356893241</v>
+        <v>264279.90344930871</v>
       </c>
     </row>
     <row r="109" spans="2:17" x14ac:dyDescent="0.25">
@@ -7941,44 +7941,44 @@
       </c>
       <c r="C110" s="10"/>
       <c r="D110" s="11">
-        <v>1671285.4699999951</v>
+        <v>1657986.3699999973</v>
       </c>
       <c r="E110" s="11">
-        <v>1092910.5499999989</v>
+        <v>1089157.7499999981</v>
       </c>
       <c r="F110" s="11">
-        <v>1459939.6999999993</v>
+        <v>1451142.7000000011</v>
       </c>
       <c r="G110" s="11">
-        <v>1084240.4699999997</v>
+        <v>1080583.0900000017</v>
       </c>
       <c r="H110" s="11">
-        <v>0</v>
+        <v>1110101.42</v>
       </c>
       <c r="I110" s="11">
-        <v>0</v>
+        <v>1385647.2599999979</v>
       </c>
       <c r="J110" s="11">
-        <v>0</v>
+        <v>1161277.5899999989</v>
       </c>
       <c r="K110" s="11">
-        <v>0</v>
+        <v>919612.46999999881</v>
       </c>
       <c r="L110" s="11">
-        <v>0</v>
+        <v>674766.05000000261</v>
       </c>
       <c r="M110" s="65">
-        <v>0</v>
+        <v>1075045.4299999997</v>
       </c>
       <c r="N110" s="11">
-        <v>0</v>
+        <v>1470932.5600000005</v>
       </c>
       <c r="O110" s="11">
         <v>0</v>
       </c>
       <c r="P110" s="6"/>
       <c r="Q110" s="65">
-        <v>5308376.1899999902</v>
+        <v>13076252.690000027</v>
       </c>
     </row>
     <row r="111" spans="2:17" x14ac:dyDescent="0.25">
@@ -7987,44 +7987,44 @@
       </c>
       <c r="C111" s="10"/>
       <c r="D111" s="21">
-        <v>9.8166898005720662E-2</v>
+        <v>9.7451186179065133E-2</v>
       </c>
       <c r="E111" s="21">
-        <v>6.9799011570212829E-2</v>
+        <v>6.957527355746955E-2</v>
       </c>
       <c r="F111" s="21">
-        <v>9.0710581298842366E-2</v>
+        <v>9.022050558304949E-2</v>
       </c>
       <c r="G111" s="21">
-        <v>7.6657139180476674E-2</v>
-      </c>
-      <c r="H111" s="21" t="s">
-        <v>211</v>
-      </c>
-      <c r="I111" s="21" t="s">
-        <v>211</v>
-      </c>
-      <c r="J111" s="21" t="s">
-        <v>211</v>
-      </c>
-      <c r="K111" s="21" t="s">
-        <v>211</v>
-      </c>
-      <c r="L111" s="21" t="s">
-        <v>211</v>
-      </c>
-      <c r="M111" s="95" t="s">
-        <v>211</v>
-      </c>
-      <c r="N111" s="21" t="s">
-        <v>211</v>
+        <v>7.6410512689753213E-2</v>
+      </c>
+      <c r="H111" s="21">
+        <v>8.1015565339152315E-2</v>
+      </c>
+      <c r="I111" s="21">
+        <v>0.10279562820712558</v>
+      </c>
+      <c r="J111" s="21">
+        <v>8.2925282086362309E-2</v>
+      </c>
+      <c r="K111" s="21">
+        <v>6.7011323127774414E-2</v>
+      </c>
+      <c r="L111" s="21">
+        <v>5.2235135302387554E-2</v>
+      </c>
+      <c r="M111" s="95">
+        <v>7.4404086689431215E-2</v>
+      </c>
+      <c r="N111" s="21">
+        <v>9.5248212714201697E-2</v>
       </c>
       <c r="O111" s="21" t="s">
         <v>211</v>
       </c>
       <c r="P111" s="22"/>
       <c r="Q111" s="95">
-        <v>8.4365180935724135E-2</v>
+        <v>8.1414686619194571E-2</v>
       </c>
     </row>
     <row r="112" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -8049,44 +8049,44 @@
         <v>202</v>
       </c>
       <c r="D113" s="11">
-        <v>17024939.199999996</v>
+        <v>17013506.299999997</v>
       </c>
       <c r="E113" s="11">
-        <v>15657965.999999998</v>
+        <v>15654379.699999999</v>
       </c>
       <c r="F113" s="11">
-        <v>16094480.699999999</v>
+        <v>16084400</v>
       </c>
       <c r="G113" s="11">
-        <v>14144024.699999999</v>
+        <v>14141811.800000001</v>
       </c>
       <c r="H113" s="11">
-        <v>0</v>
+        <v>13702322.699999999</v>
       </c>
       <c r="I113" s="11">
-        <v>0</v>
+        <v>13479632.199999997</v>
       </c>
       <c r="J113" s="11">
-        <v>0</v>
+        <v>14003902.799999999</v>
       </c>
       <c r="K113" s="11">
-        <v>0</v>
+        <v>13723239.999999998</v>
       </c>
       <c r="L113" s="11">
-        <v>0</v>
+        <v>12917857.800000003</v>
       </c>
       <c r="M113" s="65">
-        <v>0</v>
+        <v>14448741.699999999</v>
       </c>
       <c r="N113" s="11">
-        <v>0</v>
+        <v>15443151.300000001</v>
       </c>
       <c r="O113" s="11">
         <v>0</v>
       </c>
       <c r="P113" s="6"/>
       <c r="Q113" s="65">
-        <v>62921410.599999994</v>
+        <v>160612946.30000001</v>
       </c>
     </row>
     <row r="114" spans="2:17" x14ac:dyDescent="0.25">

--- a/Gas_current.xlsx
+++ b/Gas_current.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="V:\Information Management\Info Sharing and Tracking\Product Services\Operations\Product Creation\ST3\ST3s_Report_Prep\All_Pages_Content_Update\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D46289B6-91E4-4DEC-8413-274A2BF27BA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05C340A2-A114-4E5A-A042-3E87602EAD2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-19310" yWindow="1390" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Documentation" sheetId="20" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="213">
   <si>
     <t>Saskatchewan</t>
   </si>
@@ -730,13 +730,10 @@
     <t xml:space="preserve">              The opening and closing inventory volumes for natural gas are submitted voluntarily to the AER and are not a requirement (those licensees are regulated by NEB). Therefore, they do not reflect the actual amount.</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>2025</t>
   </si>
   <si>
-    <t xml:space="preserve"> Run Date:  29 December 2025</t>
+    <t xml:space="preserve"> Run Date:  27 January 2026</t>
   </si>
 </sst>
 </file>
@@ -1742,27 +1739,27 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:BI118"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="43" customWidth="1"/>
-    <col min="3" max="3" width="3.85546875" customWidth="1"/>
-    <col min="4" max="7" width="14.5703125" customWidth="1"/>
-    <col min="8" max="10" width="16.42578125" customWidth="1"/>
-    <col min="11" max="15" width="14.5703125" customWidth="1"/>
-    <col min="16" max="16" width="1.5703125" customWidth="1"/>
+    <col min="3" max="3" width="3.88671875" customWidth="1"/>
+    <col min="4" max="7" width="14.5546875" customWidth="1"/>
+    <col min="8" max="10" width="16.44140625" customWidth="1"/>
+    <col min="11" max="15" width="14.5546875" customWidth="1"/>
+    <col min="16" max="16" width="1.5546875" customWidth="1"/>
     <col min="17" max="17" width="17" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" customWidth="1"/>
-    <col min="20" max="20" width="10.42578125" customWidth="1"/>
-    <col min="21" max="21" width="18.42578125" customWidth="1"/>
+    <col min="18" max="18" width="14.5546875" customWidth="1"/>
+    <col min="20" max="20" width="10.44140625" customWidth="1"/>
+    <col min="21" max="21" width="18.44140625" customWidth="1"/>
     <col min="22" max="22" width="11" customWidth="1"/>
-    <col min="23" max="23" width="19.42578125" customWidth="1"/>
-    <col min="24" max="24" width="23.7109375" customWidth="1"/>
-    <col min="25" max="25" width="6.7109375" customWidth="1"/>
-    <col min="26" max="26" width="9.85546875" customWidth="1"/>
+    <col min="23" max="23" width="19.44140625" customWidth="1"/>
+    <col min="24" max="24" width="23.6640625" customWidth="1"/>
+    <col min="25" max="25" width="6.6640625" customWidth="1"/>
+    <col min="26" max="26" width="9.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:61" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:61" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q1"/>
       <c r="R1"/>
       <c r="S1"/>
@@ -1809,7 +1806,7 @@
       <c r="BH1"/>
       <c r="BI1"/>
     </row>
-    <row r="2" spans="1:61" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:61" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H2" s="50"/>
       <c r="I2" s="67" t="s">
         <v>25</v>
@@ -1864,7 +1861,7 @@
       <c r="BH2"/>
       <c r="BI2"/>
     </row>
-    <row r="3" spans="1:61" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:61" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H3" s="100" t="s">
         <v>204</v>
       </c>
@@ -1919,7 +1916,7 @@
       <c r="BH3"/>
       <c r="BI3"/>
     </row>
-    <row r="4" spans="1:61" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:61" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="68" t="s">
         <v>205</v>
       </c>
@@ -1943,7 +1940,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:61" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:61" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="69"/>
       <c r="C5" s="4"/>
       <c r="D5" s="3" t="s">
@@ -1987,13 +1984,13 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:61" s="2" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:61" s="2" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B6" s="70" t="s">
         <v>36</v>
       </c>
       <c r="C6" s="31"/>
     </row>
-    <row r="7" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A7" s="2"/>
       <c r="B7" s="71" t="s">
         <v>168</v>
@@ -2019,7 +2016,7 @@
       <c r="R7" s="34"/>
       <c r="S7" s="2"/>
     </row>
-    <row r="8" spans="1:61" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:61" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2"/>
       <c r="B8" s="72"/>
       <c r="D8" s="25"/>
@@ -2037,7 +2034,7 @@
       <c r="P8" s="33"/>
       <c r="Q8" s="33"/>
     </row>
-    <row r="9" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A9" s="2"/>
       <c r="B9" s="71" t="s">
         <v>125</v>
@@ -2055,7 +2052,7 @@
       <c r="AB9" s="53"/>
       <c r="AC9" s="54"/>
     </row>
-    <row r="10" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:61" x14ac:dyDescent="0.3">
       <c r="B10" s="73" t="s">
         <v>45</v>
       </c>
@@ -2090,7 +2087,7 @@
       </c>
       <c r="AC10" s="56"/>
     </row>
-    <row r="11" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:61" x14ac:dyDescent="0.3">
       <c r="B11" s="73" t="s">
         <v>60</v>
       </c>
@@ -2125,7 +2122,7 @@
       </c>
       <c r="AC11" s="56"/>
     </row>
-    <row r="12" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:61" x14ac:dyDescent="0.3">
       <c r="B12" s="73"/>
       <c r="C12" s="13"/>
       <c r="D12" s="24"/>
@@ -2171,7 +2168,7 @@
       </c>
       <c r="AC12" s="56"/>
     </row>
-    <row r="13" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:61" x14ac:dyDescent="0.3">
       <c r="B13" s="73" t="s">
         <v>46</v>
       </c>
@@ -2206,7 +2203,7 @@
       </c>
       <c r="AC13" s="56"/>
     </row>
-    <row r="14" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:61" x14ac:dyDescent="0.3">
       <c r="B14" s="73" t="s">
         <v>47</v>
       </c>
@@ -2241,7 +2238,7 @@
       </c>
       <c r="AC14" s="56"/>
     </row>
-    <row r="15" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:61" x14ac:dyDescent="0.3">
       <c r="B15" s="73" t="s">
         <v>49</v>
       </c>
@@ -2276,7 +2273,7 @@
       </c>
       <c r="AC15" s="56"/>
     </row>
-    <row r="16" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:61" x14ac:dyDescent="0.3">
       <c r="B16" s="73" t="s">
         <v>50</v>
       </c>
@@ -2311,7 +2308,7 @@
       </c>
       <c r="AC16" s="56"/>
     </row>
-    <row r="17" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B17" s="73"/>
       <c r="C17" s="13"/>
       <c r="D17" s="24"/>
@@ -2331,7 +2328,7 @@
       <c r="T17" s="57"/>
       <c r="AC17" s="56"/>
     </row>
-    <row r="18" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B18" s="73" t="s">
         <v>196</v>
       </c>
@@ -2355,7 +2352,7 @@
       <c r="T18" s="57"/>
       <c r="AC18" s="56"/>
     </row>
-    <row r="19" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B19" s="73"/>
       <c r="C19" s="13"/>
       <c r="D19" s="88"/>
@@ -2388,7 +2385,7 @@
       </c>
       <c r="AC19" s="56"/>
     </row>
-    <row r="20" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B20" s="73" t="s">
         <v>51</v>
       </c>
@@ -2423,7 +2420,7 @@
       </c>
       <c r="AC20" s="56"/>
     </row>
-    <row r="21" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B21" s="73" t="s">
         <v>48</v>
       </c>
@@ -2457,7 +2454,7 @@
       </c>
       <c r="AC21" s="56"/>
     </row>
-    <row r="22" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B22" s="74" t="s">
         <v>126</v>
       </c>
@@ -2478,7 +2475,7 @@
       </c>
       <c r="AC22" s="56"/>
     </row>
-    <row r="23" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B23" s="74"/>
       <c r="D23" s="25"/>
       <c r="T23" s="57">
@@ -2495,7 +2492,7 @@
       </c>
       <c r="AC23" s="56"/>
     </row>
-    <row r="24" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B24" s="74" t="s">
         <v>127</v>
       </c>
@@ -2514,7 +2511,7 @@
       </c>
       <c r="AC24" s="56"/>
     </row>
-    <row r="25" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B25" s="73" t="s">
         <v>56</v>
       </c>
@@ -2536,7 +2533,7 @@
       </c>
       <c r="AC25" s="56"/>
     </row>
-    <row r="26" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B26" s="73" t="s">
         <v>67</v>
       </c>
@@ -2558,7 +2555,7 @@
       </c>
       <c r="AC26" s="56"/>
     </row>
-    <row r="27" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B27" s="73" t="s">
         <v>73</v>
       </c>
@@ -2580,7 +2577,7 @@
       </c>
       <c r="AC27" s="56"/>
     </row>
-    <row r="28" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B28" s="73" t="s">
         <v>70</v>
       </c>
@@ -2602,7 +2599,7 @@
       </c>
       <c r="AC28" s="56"/>
     </row>
-    <row r="29" spans="2:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B29" s="73" t="s">
         <v>69</v>
       </c>
@@ -2629,7 +2626,7 @@
       <c r="AB29" s="59"/>
       <c r="AC29" s="60"/>
     </row>
-    <row r="30" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B30" s="73" t="s">
         <v>68</v>
       </c>
@@ -2650,7 +2647,7 @@
       <c r="O30" s="27"/>
       <c r="Q30" s="27"/>
     </row>
-    <row r="31" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B31" s="74" t="s">
         <v>128</v>
       </c>
@@ -2659,12 +2656,12 @@
         <v>76</v>
       </c>
     </row>
-    <row r="32" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B32" s="74"/>
       <c r="C32" s="14"/>
       <c r="D32" s="25"/>
     </row>
-    <row r="33" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A33"/>
       <c r="B33" s="71" t="s">
         <v>129</v>
@@ -2673,7 +2670,7 @@
       <c r="D33"/>
       <c r="T33"/>
     </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B34" s="73" t="s">
         <v>38</v>
       </c>
@@ -2683,7 +2680,7 @@
       </c>
       <c r="T34" s="2"/>
     </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B35" s="73" t="s">
         <v>39</v>
       </c>
@@ -2692,7 +2689,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B36" s="73" t="s">
         <v>40</v>
       </c>
@@ -2701,7 +2698,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B37" s="73" t="s">
         <v>33</v>
       </c>
@@ -2710,23 +2707,23 @@
         <v>123</v>
       </c>
     </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B38" s="74" t="s">
         <v>130</v>
       </c>
       <c r="C38" s="14"/>
     </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B39" s="74"/>
       <c r="C39" s="14"/>
     </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B40" s="71" t="s">
         <v>57</v>
       </c>
       <c r="C40" s="14"/>
     </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B41" s="73" t="s">
         <v>38</v>
       </c>
@@ -2748,7 +2745,7 @@
       <c r="Q41" s="36"/>
       <c r="R41" s="34"/>
     </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B42" s="73" t="s">
         <v>39</v>
       </c>
@@ -2769,7 +2766,7 @@
       <c r="P42" s="33"/>
       <c r="Q42" s="33"/>
     </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B43" s="73" t="s">
         <v>40</v>
       </c>
@@ -2790,7 +2787,7 @@
       <c r="P43" s="37"/>
       <c r="Q43" s="37"/>
     </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B44" s="73" t="s">
         <v>33</v>
       </c>
@@ -2811,7 +2808,7 @@
       <c r="P44" s="38"/>
       <c r="Q44" s="38"/>
     </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B45" s="73" t="s">
         <v>54</v>
       </c>
@@ -2832,7 +2829,7 @@
       <c r="P45" s="33"/>
       <c r="Q45" s="33"/>
     </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B46" s="74" t="s">
         <v>58</v>
       </c>
@@ -2851,10 +2848,10 @@
       <c r="P46" s="33"/>
       <c r="Q46" s="33"/>
     </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B47" s="74"/>
     </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B48" s="71" t="s">
         <v>169</v>
       </c>
@@ -2879,7 +2876,7 @@
       </c>
       <c r="R48" s="34"/>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B49" s="71" t="s">
         <v>167</v>
       </c>
@@ -2901,7 +2898,7 @@
       <c r="P49" s="33"/>
       <c r="Q49" s="25"/>
     </row>
-    <row r="50" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B50" s="71"/>
       <c r="C50" s="13"/>
       <c r="D50" s="40"/>
@@ -2919,7 +2916,7 @@
       <c r="P50" s="33"/>
       <c r="Q50" s="40"/>
     </row>
-    <row r="51" spans="1:17" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:17" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B51" s="75" t="s">
         <v>200</v>
       </c>
@@ -2941,7 +2938,7 @@
       <c r="P51" s="38"/>
       <c r="Q51" s="38"/>
     </row>
-    <row r="52" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B52" s="68" t="s">
         <v>205</v>
       </c>
@@ -2962,7 +2959,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="53" spans="1:17" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:17" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B53" s="69"/>
       <c r="C53" s="4"/>
       <c r="D53" s="90" t="s">
@@ -3006,7 +3003,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B54" s="72" t="s">
         <v>37</v>
       </c>
@@ -3026,7 +3023,7 @@
       <c r="P54" s="33"/>
       <c r="Q54" s="33"/>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B55" s="71" t="s">
         <v>34</v>
       </c>
@@ -3046,7 +3043,7 @@
       <c r="P55" s="33"/>
       <c r="Q55" s="33"/>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B56" s="73" t="s">
         <v>26</v>
       </c>
@@ -3055,7 +3052,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A57" s="2"/>
       <c r="B57" s="73" t="s">
         <v>27</v>
@@ -3065,7 +3062,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B58" s="73" t="s">
         <v>59</v>
       </c>
@@ -3074,11 +3071,11 @@
         <v>104</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B59" s="73"/>
       <c r="C59" s="13"/>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B60" s="73" t="s">
         <v>53</v>
       </c>
@@ -3087,7 +3084,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B61" s="73" t="s">
         <v>71</v>
       </c>
@@ -3096,17 +3093,17 @@
         <v>105</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B62" s="73"/>
       <c r="C62" s="13"/>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B63" s="73" t="s">
         <v>72</v>
       </c>
       <c r="C63" s="15"/>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B64" s="76" t="s">
         <v>41</v>
       </c>
@@ -3115,7 +3112,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B65" s="76" t="s">
         <v>42</v>
       </c>
@@ -3124,7 +3121,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B66" s="76" t="s">
         <v>44</v>
       </c>
@@ -3133,7 +3130,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B67" s="76" t="s">
         <v>43</v>
       </c>
@@ -3154,7 +3151,7 @@
       <c r="O67" s="27"/>
       <c r="Q67" s="27"/>
     </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B68" s="73" t="s">
         <v>52</v>
       </c>
@@ -3176,17 +3173,17 @@
       <c r="P68" s="33"/>
       <c r="Q68" s="33"/>
     </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B69" s="77"/>
       <c r="C69" s="15"/>
     </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B70" s="73" t="s">
         <v>62</v>
       </c>
       <c r="C70" s="13"/>
     </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B71" s="76" t="s">
         <v>61</v>
       </c>
@@ -3195,7 +3192,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B72" s="76" t="s">
         <v>38</v>
       </c>
@@ -3204,7 +3201,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B73" s="76" t="s">
         <v>39</v>
       </c>
@@ -3213,7 +3210,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B74" s="76" t="s">
         <v>40</v>
       </c>
@@ -3234,7 +3231,7 @@
       <c r="O74" s="27"/>
       <c r="Q74" s="27"/>
     </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B75" s="73" t="s">
         <v>63</v>
       </c>
@@ -3256,17 +3253,17 @@
       <c r="P75" s="33"/>
       <c r="Q75" s="33"/>
     </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B76" s="77"/>
       <c r="C76" s="15"/>
     </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B77" s="73" t="s">
         <v>64</v>
       </c>
       <c r="C77" s="13"/>
     </row>
-    <row r="78" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B78" s="76" t="s">
         <v>38</v>
       </c>
@@ -3275,7 +3272,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B79" s="76" t="s">
         <v>39</v>
       </c>
@@ -3284,7 +3281,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B80" s="76" t="s">
         <v>66</v>
       </c>
@@ -3305,7 +3302,7 @@
       <c r="O80" s="27"/>
       <c r="Q80" s="27"/>
     </row>
-    <row r="81" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B81" s="73" t="s">
         <v>65</v>
       </c>
@@ -3327,7 +3324,7 @@
       <c r="P81" s="33"/>
       <c r="Q81" s="33"/>
     </row>
-    <row r="82" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B82" s="77"/>
       <c r="C82" s="15"/>
       <c r="D82" s="49"/>
@@ -3344,7 +3341,7 @@
       <c r="O82" s="49"/>
       <c r="Q82" s="49"/>
     </row>
-    <row r="83" spans="2:17" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:17" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B83" s="74" t="s">
         <v>35</v>
       </c>
@@ -3366,17 +3363,17 @@
       <c r="P83" s="33"/>
       <c r="Q83" s="33"/>
     </row>
-    <row r="84" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B84" s="78"/>
       <c r="C84" s="13"/>
     </row>
-    <row r="85" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B85" s="71" t="s">
         <v>171</v>
       </c>
       <c r="C85" s="14"/>
     </row>
-    <row r="86" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B86" s="73" t="s">
         <v>5</v>
       </c>
@@ -3390,7 +3387,7 @@
       <c r="H86" s="32"/>
       <c r="I86" s="32"/>
     </row>
-    <row r="87" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B87" s="73" t="s">
         <v>0</v>
       </c>
@@ -3398,7 +3395,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="88" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B88" s="73" t="s">
         <v>1</v>
       </c>
@@ -3416,7 +3413,7 @@
       <c r="P88" s="33"/>
       <c r="Q88" s="33"/>
     </row>
-    <row r="89" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B89" s="73" t="s">
         <v>2</v>
       </c>
@@ -3438,7 +3435,7 @@
       <c r="P89" s="33"/>
       <c r="Q89" s="33"/>
     </row>
-    <row r="90" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B90" s="73" t="s">
         <v>3</v>
       </c>
@@ -3460,7 +3457,7 @@
       <c r="P90" s="33"/>
       <c r="Q90" s="33"/>
     </row>
-    <row r="91" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B91" s="73" t="s">
         <v>4</v>
       </c>
@@ -3482,7 +3479,7 @@
       <c r="P91" s="33"/>
       <c r="Q91" s="33"/>
     </row>
-    <row r="92" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B92" s="73" t="s">
         <v>55</v>
       </c>
@@ -3504,7 +3501,7 @@
       <c r="P92" s="33"/>
       <c r="Q92" s="43"/>
     </row>
-    <row r="93" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B93" s="74" t="s">
         <v>172</v>
       </c>
@@ -3526,7 +3523,7 @@
       <c r="P93" s="33"/>
       <c r="Q93" s="33"/>
     </row>
-    <row r="94" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B94" s="78"/>
       <c r="C94" s="13"/>
       <c r="D94" s="25"/>
@@ -3544,7 +3541,7 @@
       <c r="P94" s="33"/>
       <c r="Q94" s="33"/>
     </row>
-    <row r="95" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B95" s="79" t="s">
         <v>173</v>
       </c>
@@ -3564,7 +3561,7 @@
       <c r="P95" s="33"/>
       <c r="Q95" s="33"/>
     </row>
-    <row r="96" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B96" s="80" t="s">
         <v>28</v>
       </c>
@@ -3585,7 +3582,7 @@
       <c r="P96" s="46"/>
       <c r="Q96" s="46"/>
     </row>
-    <row r="97" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B97" s="80" t="s">
         <v>29</v>
       </c>
@@ -3607,7 +3604,7 @@
       <c r="P97" s="46"/>
       <c r="Q97" s="46"/>
     </row>
-    <row r="98" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B98" s="80" t="s">
         <v>30</v>
       </c>
@@ -3629,7 +3626,7 @@
       <c r="P98" s="46"/>
       <c r="Q98" s="46"/>
     </row>
-    <row r="99" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B99" s="80" t="s">
         <v>31</v>
       </c>
@@ -3651,7 +3648,7 @@
       <c r="P99" s="33"/>
       <c r="Q99" s="33"/>
     </row>
-    <row r="100" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B100" s="80" t="s">
         <v>32</v>
       </c>
@@ -3673,7 +3670,7 @@
       <c r="P100" s="33"/>
       <c r="Q100" s="43"/>
     </row>
-    <row r="101" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B101" s="81" t="s">
         <v>174</v>
       </c>
@@ -3695,7 +3692,7 @@
       <c r="P101" s="33"/>
       <c r="Q101" s="33"/>
     </row>
-    <row r="102" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B102" s="82"/>
       <c r="C102" s="45"/>
       <c r="D102" s="25"/>
@@ -3713,7 +3710,7 @@
       <c r="P102" s="33"/>
       <c r="Q102" s="33"/>
     </row>
-    <row r="103" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B103" s="81" t="s">
         <v>170</v>
       </c>
@@ -3735,7 +3732,7 @@
       <c r="P103" s="33"/>
       <c r="Q103" s="33"/>
     </row>
-    <row r="104" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B104" s="68" t="s">
         <v>206</v>
       </c>
@@ -3756,7 +3753,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="105" spans="2:17" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:17" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B105" s="69"/>
       <c r="C105" s="4"/>
       <c r="D105" s="90" t="s">
@@ -3800,7 +3797,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="106" spans="2:17" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="2:17" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B106" s="69"/>
       <c r="C106" s="4"/>
       <c r="D106" s="92"/>
@@ -3818,7 +3815,7 @@
       <c r="P106" s="61"/>
       <c r="Q106" s="61"/>
     </row>
-    <row r="107" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B107" s="79" t="s">
         <v>165</v>
       </c>
@@ -3840,7 +3837,7 @@
       <c r="P107" s="33"/>
       <c r="Q107" s="33"/>
     </row>
-    <row r="108" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B108" s="83" t="s">
         <v>201</v>
       </c>
@@ -3864,7 +3861,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="109" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B109" s="84"/>
       <c r="C109" s="41"/>
       <c r="D109" s="25"/>
@@ -3882,7 +3879,7 @@
       <c r="P109" s="33"/>
       <c r="Q109" s="33"/>
     </row>
-    <row r="110" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B110" s="79" t="s">
         <v>6</v>
       </c>
@@ -3904,7 +3901,7 @@
       <c r="P110" s="48"/>
       <c r="Q110" s="48"/>
     </row>
-    <row r="111" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="111" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B111" s="85" t="s">
         <v>166</v>
       </c>
@@ -3926,7 +3923,7 @@
       <c r="P111" s="33"/>
       <c r="Q111" s="33"/>
     </row>
-    <row r="112" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B112" s="71"/>
       <c r="C112" s="44"/>
       <c r="D112" s="49"/>
@@ -3943,7 +3940,7 @@
       <c r="O112" s="49"/>
       <c r="Q112" s="49"/>
     </row>
-    <row r="113" spans="2:17" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="2:17" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B113" s="86" t="s">
         <v>202</v>
       </c>
@@ -3965,23 +3962,23 @@
       <c r="P113" s="38"/>
       <c r="Q113" s="38"/>
     </row>
-    <row r="114" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="114" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B114" s="71"/>
     </row>
-    <row r="115" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B115" s="71"/>
     </row>
-    <row r="116" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="116" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B116" s="87" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="117" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="117" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B117" s="87" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="118" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="118" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B118" s="87" t="s">
         <v>210</v>
       </c>
@@ -4005,20 +4002,20 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:Q118"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="43" customWidth="1"/>
-    <col min="3" max="3" width="3.85546875" customWidth="1"/>
-    <col min="4" max="15" width="15.7109375" customWidth="1"/>
-    <col min="16" max="16" width="1.5703125" customWidth="1"/>
+    <col min="3" max="3" width="3.88671875" customWidth="1"/>
+    <col min="4" max="15" width="15.6640625" customWidth="1"/>
+    <col min="16" max="16" width="1.5546875" customWidth="1"/>
     <col min="17" max="17" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:17" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:17" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q1"/>
     </row>
-    <row r="2" spans="2:17" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:17" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H2" s="50"/>
       <c r="I2" s="67" t="s">
         <v>25</v>
@@ -4026,7 +4023,7 @@
       <c r="J2" s="51"/>
       <c r="Q2"/>
     </row>
-    <row r="3" spans="2:17" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:17" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H3" s="100" t="s">
         <v>204</v>
       </c>
@@ -4034,9 +4031,9 @@
       <c r="J3" s="102"/>
       <c r="Q3"/>
     </row>
-    <row r="4" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="93" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C4" s="20"/>
       <c r="D4" s="2"/>
@@ -4056,7 +4053,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="2:17" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:17" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="69"/>
       <c r="C5" s="4"/>
       <c r="D5" s="3" t="s">
@@ -4097,16 +4094,16 @@
       </c>
       <c r="P5" s="3"/>
       <c r="Q5" s="3" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="6" spans="2:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="6" spans="2:17" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B6" s="72" t="s">
         <v>36</v>
       </c>
       <c r="C6" s="17"/>
     </row>
-    <row r="7" spans="2:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:17" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B7" s="71" t="s">
         <v>168</v>
       </c>
@@ -4145,18 +4142,18 @@
         <v>554102</v>
       </c>
       <c r="O7" s="11">
-        <v>0</v>
+        <v>564451.5</v>
       </c>
       <c r="P7" s="6"/>
       <c r="Q7" s="6">
         <v>601778.1</v>
       </c>
     </row>
-    <row r="8" spans="2:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:17" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B8" s="72"/>
       <c r="C8" s="17"/>
     </row>
-    <row r="9" spans="2:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:17" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B9" s="71" t="s">
         <v>125</v>
       </c>
@@ -4176,53 +4173,53 @@
       <c r="P9" s="6"/>
       <c r="Q9" s="6"/>
     </row>
-    <row r="10" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B10" s="73" t="s">
         <v>45</v>
       </c>
       <c r="C10" s="13"/>
       <c r="D10" s="11">
-        <v>11596020.6</v>
+        <v>11596059.199999999</v>
       </c>
       <c r="E10" s="11">
-        <v>10229168.199999999</v>
+        <v>10229216</v>
       </c>
       <c r="F10" s="11">
-        <v>11696781.800000001</v>
+        <v>11696829.300000001</v>
       </c>
       <c r="G10" s="11">
-        <v>11239507.4</v>
+        <v>11239573.5</v>
       </c>
       <c r="H10" s="11">
-        <v>11398845.199999999</v>
+        <v>11398928.5</v>
       </c>
       <c r="I10" s="11">
-        <v>10672542.699999999</v>
+        <v>10672570.5</v>
       </c>
       <c r="J10" s="11">
-        <v>11248025</v>
+        <v>11248057.300000001</v>
       </c>
       <c r="K10" s="11">
-        <v>11200434.199999999</v>
+        <v>11200490.9</v>
       </c>
       <c r="L10" s="11">
-        <v>10849935.9</v>
+        <v>10849817.4</v>
       </c>
       <c r="M10" s="11">
-        <v>11492513.4</v>
+        <v>11492368.6</v>
       </c>
       <c r="N10" s="11">
-        <v>11507511.6</v>
+        <v>11508077.1</v>
       </c>
       <c r="O10" s="11">
-        <v>0</v>
+        <v>11824739.1</v>
       </c>
       <c r="P10" s="6"/>
       <c r="Q10" s="6">
-        <v>123131286.00000001</v>
-      </c>
-    </row>
-    <row r="11" spans="2:17" x14ac:dyDescent="0.25">
+        <v>134956727.40000001</v>
+      </c>
+    </row>
+    <row r="11" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B11" s="73" t="s">
         <v>60</v>
       </c>
@@ -4255,20 +4252,20 @@
         <v>331771.3</v>
       </c>
       <c r="M11" s="11">
-        <v>346804.6</v>
+        <v>346982.1</v>
       </c>
       <c r="N11" s="11">
-        <v>339251.8</v>
+        <v>339252.7</v>
       </c>
       <c r="O11" s="11">
-        <v>0</v>
+        <v>353036.9</v>
       </c>
       <c r="P11" s="6"/>
       <c r="Q11" s="6">
-        <v>3510281.6</v>
-      </c>
-    </row>
-    <row r="12" spans="2:17" x14ac:dyDescent="0.25">
+        <v>3863496.9000000004</v>
+      </c>
+    </row>
+    <row r="12" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B12" s="73"/>
       <c r="C12" s="13"/>
       <c r="D12" s="11"/>
@@ -4286,7 +4283,7 @@
       <c r="P12" s="6"/>
       <c r="Q12" s="6"/>
     </row>
-    <row r="13" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B13" s="73" t="s">
         <v>46</v>
       </c>
@@ -4322,17 +4319,17 @@
         <v>72634.2</v>
       </c>
       <c r="N13" s="11">
-        <v>337876.8</v>
+        <v>337876.7</v>
       </c>
       <c r="O13" s="11">
-        <v>0</v>
+        <v>1759152.9</v>
       </c>
       <c r="P13" s="6"/>
       <c r="Q13" s="6">
-        <v>4094444.9</v>
-      </c>
-    </row>
-    <row r="14" spans="2:17" x14ac:dyDescent="0.25">
+        <v>5853597.7000000002</v>
+      </c>
+    </row>
+    <row r="14" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B14" s="73" t="s">
         <v>47</v>
       </c>
@@ -4371,14 +4368,14 @@
         <v>-117125.5</v>
       </c>
       <c r="O14" s="11">
-        <v>0</v>
+        <v>-6712.9</v>
       </c>
       <c r="P14" s="6"/>
       <c r="Q14" s="6">
-        <v>-5611166.8000000007</v>
-      </c>
-    </row>
-    <row r="15" spans="2:17" x14ac:dyDescent="0.25">
+        <v>-5617879.7000000011</v>
+      </c>
+    </row>
+    <row r="15" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B15" s="73" t="s">
         <v>49</v>
       </c>
@@ -4417,14 +4414,14 @@
         <v>541.4</v>
       </c>
       <c r="O15" s="11">
-        <v>0</v>
+        <v>698</v>
       </c>
       <c r="P15" s="6"/>
       <c r="Q15" s="6">
-        <v>9327</v>
-      </c>
-    </row>
-    <row r="16" spans="2:17" x14ac:dyDescent="0.25">
+        <v>10025</v>
+      </c>
+    </row>
+    <row r="16" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B16" s="73" t="s">
         <v>50</v>
       </c>
@@ -4463,14 +4460,14 @@
         <v>-14008.1</v>
       </c>
       <c r="O16" s="11">
-        <v>0</v>
+        <v>-12514.4</v>
       </c>
       <c r="P16" s="6"/>
       <c r="Q16" s="6">
-        <v>-166139.20000000001</v>
-      </c>
-    </row>
-    <row r="17" spans="2:17" x14ac:dyDescent="0.25">
+        <v>-178653.6</v>
+      </c>
+    </row>
+    <row r="17" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B17" s="73"/>
       <c r="C17" s="13"/>
       <c r="D17" s="9"/>
@@ -4488,53 +4485,53 @@
       <c r="P17" s="6"/>
       <c r="Q17" s="7"/>
     </row>
-    <row r="18" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B18" s="73" t="s">
         <v>196</v>
       </c>
       <c r="C18" s="13"/>
       <c r="D18" s="11">
-        <v>13191048.299999999</v>
+        <v>13191086.899999999</v>
       </c>
       <c r="E18" s="11">
-        <v>12245932</v>
+        <v>12245979.800000001</v>
       </c>
       <c r="F18" s="11">
-        <v>12508895.000000002</v>
+        <v>12508942.500000002</v>
       </c>
       <c r="G18" s="11">
-        <v>10863183.399999999</v>
+        <v>10863249.499999998</v>
       </c>
       <c r="H18" s="11">
-        <v>10246393.799999999</v>
+        <v>10246477.1</v>
       </c>
       <c r="I18" s="11">
-        <v>10182202.399999999</v>
+        <v>10182230.199999999</v>
       </c>
       <c r="J18" s="11">
-        <v>10765031.6</v>
+        <v>10765063.9</v>
       </c>
       <c r="K18" s="11">
-        <v>10880021</v>
+        <v>10880077.700000001</v>
       </c>
       <c r="L18" s="11">
-        <v>10471632.200000001</v>
+        <v>10471513.700000001</v>
       </c>
       <c r="M18" s="11">
-        <v>11559645.799999999</v>
+        <v>11559678.499999998</v>
       </c>
       <c r="N18" s="11">
-        <v>12054048.000000002</v>
+        <v>12054614.299999999</v>
       </c>
       <c r="O18" s="11">
-        <v>0</v>
+        <v>13918399.6</v>
       </c>
       <c r="P18" s="6"/>
       <c r="Q18" s="11">
-        <v>124968033.50000001</v>
-      </c>
-    </row>
-    <row r="19" spans="2:17" x14ac:dyDescent="0.25">
+        <v>138887313.70000002</v>
+      </c>
+    </row>
+    <row r="19" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B19" s="73"/>
       <c r="C19" s="13"/>
       <c r="D19" s="11"/>
@@ -4552,7 +4549,7 @@
       <c r="P19" s="6"/>
       <c r="Q19" s="6"/>
     </row>
-    <row r="20" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B20" s="73" t="s">
         <v>51</v>
       </c>
@@ -4591,14 +4588,14 @@
         <v>539172.6</v>
       </c>
       <c r="O20" s="11">
-        <v>0</v>
+        <v>553605.1</v>
       </c>
       <c r="P20" s="6"/>
       <c r="Q20" s="6">
-        <v>5499859.6999999993</v>
-      </c>
-    </row>
-    <row r="21" spans="2:17" x14ac:dyDescent="0.25">
+        <v>6053464.7999999989</v>
+      </c>
+    </row>
+    <row r="21" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B21" s="73" t="s">
         <v>48</v>
       </c>
@@ -4637,60 +4634,60 @@
         <v>351740</v>
       </c>
       <c r="O21" s="9">
-        <v>0</v>
+        <v>343955.5</v>
       </c>
       <c r="P21" s="6"/>
       <c r="Q21" s="7">
-        <v>3889019.4999999995</v>
-      </c>
-    </row>
-    <row r="22" spans="2:17" x14ac:dyDescent="0.25">
+        <v>4232975</v>
+      </c>
+    </row>
+    <row r="22" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B22" s="74" t="s">
         <v>126</v>
       </c>
       <c r="C22" s="14"/>
       <c r="D22" s="11">
-        <v>14125007.899999999</v>
+        <v>14125046.499999998</v>
       </c>
       <c r="E22" s="11">
-        <v>13054243.299999999</v>
+        <v>13054291.1</v>
       </c>
       <c r="F22" s="11">
-        <v>13420388.000000002</v>
+        <v>13420435.500000002</v>
       </c>
       <c r="G22" s="11">
-        <v>11693537.699999999</v>
+        <v>11693603.799999999</v>
       </c>
       <c r="H22" s="11">
-        <v>11008949.199999997</v>
+        <v>11009032.499999998</v>
       </c>
       <c r="I22" s="11">
-        <v>10909104.499999998</v>
+        <v>10909132.299999999</v>
       </c>
       <c r="J22" s="11">
-        <v>11658426.699999999</v>
+        <v>11658459</v>
       </c>
       <c r="K22" s="11">
-        <v>11757740.4</v>
+        <v>11757797.100000001</v>
       </c>
       <c r="L22" s="11">
-        <v>11322408.200000001</v>
+        <v>11322289.700000001</v>
       </c>
       <c r="M22" s="11">
-        <v>12462146.199999999</v>
+        <v>12462178.899999999</v>
       </c>
       <c r="N22" s="11">
-        <v>12944960.600000001</v>
+        <v>12945526.899999999</v>
       </c>
       <c r="O22" s="11">
-        <v>0</v>
+        <v>14815960.199999999</v>
       </c>
       <c r="P22" s="6"/>
       <c r="Q22" s="11">
-        <v>134356912.70000002</v>
-      </c>
-    </row>
-    <row r="23" spans="2:17" x14ac:dyDescent="0.25">
+        <v>149173753.50000003</v>
+      </c>
+    </row>
+    <row r="23" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B23" s="74"/>
       <c r="C23" s="14"/>
       <c r="D23" s="11"/>
@@ -4708,7 +4705,7 @@
       <c r="P23" s="6"/>
       <c r="Q23" s="11"/>
     </row>
-    <row r="24" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B24" s="74" t="s">
         <v>127</v>
       </c>
@@ -4728,7 +4725,7 @@
       <c r="P24" s="6"/>
       <c r="Q24" s="6"/>
     </row>
-    <row r="25" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B25" s="73" t="s">
         <v>56</v>
       </c>
@@ -4761,20 +4758,20 @@
         <v>636.1</v>
       </c>
       <c r="M25" s="11">
-        <v>761.7</v>
+        <v>773.3</v>
       </c>
       <c r="N25" s="11">
         <v>732.3</v>
       </c>
       <c r="O25" s="11">
-        <v>0</v>
+        <v>683.4</v>
       </c>
       <c r="P25" s="6"/>
       <c r="Q25" s="6">
-        <v>7979.6</v>
-      </c>
-    </row>
-    <row r="26" spans="2:17" x14ac:dyDescent="0.25">
+        <v>8674.6</v>
+      </c>
+    </row>
+    <row r="26" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B26" s="73" t="s">
         <v>67</v>
       </c>
@@ -4813,14 +4810,14 @@
         <v>48823.3</v>
       </c>
       <c r="O26" s="11">
-        <v>0</v>
+        <v>52624.1</v>
       </c>
       <c r="P26" s="6"/>
       <c r="Q26" s="6">
-        <v>541336.5</v>
-      </c>
-    </row>
-    <row r="27" spans="2:17" x14ac:dyDescent="0.25">
+        <v>593960.6</v>
+      </c>
+    </row>
+    <row r="27" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B27" s="73" t="s">
         <v>73</v>
       </c>
@@ -4844,7 +4841,7 @@
         <v>215926.6</v>
       </c>
       <c r="J27" s="11">
-        <v>201170.3</v>
+        <v>201171.4</v>
       </c>
       <c r="K27" s="11">
         <v>206830.3</v>
@@ -4859,14 +4856,14 @@
         <v>252749.2</v>
       </c>
       <c r="O27" s="11">
-        <v>0</v>
+        <v>256938.6</v>
       </c>
       <c r="P27" s="6"/>
       <c r="Q27" s="6">
-        <v>2588379.8000000003</v>
-      </c>
-    </row>
-    <row r="28" spans="2:17" x14ac:dyDescent="0.25">
+        <v>2845319.5000000005</v>
+      </c>
+    </row>
+    <row r="28" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B28" s="73" t="s">
         <v>70</v>
       </c>
@@ -4905,60 +4902,60 @@
         <v>593740.6</v>
       </c>
       <c r="O28" s="11">
-        <v>0</v>
+        <v>719754</v>
       </c>
       <c r="P28" s="6"/>
       <c r="Q28" s="6">
-        <v>5976447.7999999998</v>
-      </c>
-    </row>
-    <row r="29" spans="2:17" x14ac:dyDescent="0.25">
+        <v>6696201.7999999998</v>
+      </c>
+    </row>
+    <row r="29" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B29" s="73" t="s">
         <v>69</v>
       </c>
       <c r="C29" s="13"/>
       <c r="D29" s="11">
-        <v>134615.9</v>
+        <v>134635.6</v>
       </c>
       <c r="E29" s="11">
-        <v>126886</v>
+        <v>126910.1</v>
       </c>
       <c r="F29" s="11">
-        <v>134416.5</v>
+        <v>134451.9</v>
       </c>
       <c r="G29" s="11">
-        <v>123964.8</v>
+        <v>123992.9</v>
       </c>
       <c r="H29" s="11">
-        <v>116987.3</v>
+        <v>117010.7</v>
       </c>
       <c r="I29" s="11">
-        <v>85521.4</v>
+        <v>85546.3</v>
       </c>
       <c r="J29" s="11">
-        <v>64180.800000000003</v>
+        <v>64266.1</v>
       </c>
       <c r="K29" s="11">
-        <v>85770.2</v>
+        <v>85787.9</v>
       </c>
       <c r="L29" s="11">
-        <v>116351.2</v>
+        <v>116367.9</v>
       </c>
       <c r="M29" s="11">
-        <v>119156</v>
+        <v>119218.8</v>
       </c>
       <c r="N29" s="11">
-        <v>130881</v>
+        <v>130876</v>
       </c>
       <c r="O29" s="11">
-        <v>0</v>
+        <v>127042</v>
       </c>
       <c r="P29" s="6"/>
       <c r="Q29" s="6">
-        <v>1238731.1000000001</v>
-      </c>
-    </row>
-    <row r="30" spans="2:17" x14ac:dyDescent="0.25">
+        <v>1366106.2</v>
+      </c>
+    </row>
+    <row r="30" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B30" s="73" t="s">
         <v>68</v>
       </c>
@@ -4997,60 +4994,60 @@
         <v>3803988.8</v>
       </c>
       <c r="O30" s="64">
-        <v>0</v>
+        <v>3933104.4</v>
       </c>
       <c r="P30" s="6"/>
       <c r="Q30" s="7">
-        <v>40548743.799999997</v>
-      </c>
-    </row>
-    <row r="31" spans="2:17" x14ac:dyDescent="0.25">
+        <v>44481848.199999996</v>
+      </c>
+    </row>
+    <row r="31" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B31" s="74" t="s">
         <v>128</v>
       </c>
       <c r="C31" s="14"/>
       <c r="D31" s="11">
-        <v>5198528.0999999996</v>
+        <v>5198547.8</v>
       </c>
       <c r="E31" s="11">
-        <v>4758806.3</v>
+        <v>4758830.4000000004</v>
       </c>
       <c r="F31" s="11">
-        <v>5044115.5999999996</v>
+        <v>5044151</v>
       </c>
       <c r="G31" s="11">
-        <v>4608689.2</v>
+        <v>4608717.3</v>
       </c>
       <c r="H31" s="11">
-        <v>4957883.5</v>
+        <v>4957906.8999999994</v>
       </c>
       <c r="I31" s="11">
-        <v>4650846.4000000004</v>
+        <v>4650871.3</v>
       </c>
       <c r="J31" s="11">
-        <v>4568770.9000000004</v>
+        <v>4568857.3</v>
       </c>
       <c r="K31" s="11">
-        <v>4243475.4000000004</v>
+        <v>4243493.1000000006</v>
       </c>
       <c r="L31" s="11">
-        <v>3749373.9</v>
+        <v>3749390.6</v>
       </c>
       <c r="M31" s="11">
-        <v>4290214.0999999996</v>
+        <v>4290288.5</v>
       </c>
       <c r="N31" s="11">
-        <v>4830915.2</v>
+        <v>4830910.2</v>
       </c>
       <c r="O31" s="11">
-        <v>0</v>
+        <v>5090146.5</v>
       </c>
       <c r="P31" s="6"/>
       <c r="Q31" s="11">
-        <v>50901618.599999994</v>
-      </c>
-    </row>
-    <row r="32" spans="2:17" x14ac:dyDescent="0.25">
+        <v>55992110.899999991</v>
+      </c>
+    </row>
+    <row r="32" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B32" s="74"/>
       <c r="C32" s="14"/>
       <c r="D32" s="11"/>
@@ -5068,7 +5065,7 @@
       <c r="P32" s="6"/>
       <c r="Q32" s="11"/>
     </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B33" s="71" t="s">
         <v>129</v>
       </c>
@@ -5087,145 +5084,145 @@
       <c r="P33" s="6"/>
       <c r="Q33" s="6"/>
     </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B34" s="73" t="s">
         <v>38</v>
       </c>
       <c r="C34" s="13"/>
       <c r="D34" s="11">
-        <v>96529.600000000006</v>
+        <v>96554.5</v>
       </c>
       <c r="E34" s="11">
-        <v>92313.7</v>
+        <v>92360.6</v>
       </c>
       <c r="F34" s="11">
-        <v>96383.2</v>
+        <v>96437.7</v>
       </c>
       <c r="G34" s="11">
-        <v>93404.2</v>
+        <v>93474.8</v>
       </c>
       <c r="H34" s="11">
-        <v>97324.800000000003</v>
+        <v>97370.6</v>
       </c>
       <c r="I34" s="11">
-        <v>91134.1</v>
+        <v>91172</v>
       </c>
       <c r="J34" s="11">
-        <v>92466.1</v>
+        <v>92516.4</v>
       </c>
       <c r="K34" s="11">
-        <v>97158.9</v>
+        <v>97193.4</v>
       </c>
       <c r="L34" s="11">
-        <v>93145.3</v>
+        <v>93188.7</v>
       </c>
       <c r="M34" s="11">
-        <v>92344.4</v>
+        <v>92898</v>
       </c>
       <c r="N34" s="11">
-        <v>89247.9</v>
+        <v>89113.2</v>
       </c>
       <c r="O34" s="11">
-        <v>0</v>
+        <v>95342</v>
       </c>
       <c r="P34" s="6"/>
       <c r="Q34" s="6">
-        <v>1031452.2000000001</v>
-      </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.25">
+        <v>1127621.8999999999</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B35" s="73" t="s">
         <v>39</v>
       </c>
       <c r="C35" s="13"/>
       <c r="D35" s="11">
-        <v>781164.1</v>
+        <v>781490.6</v>
       </c>
       <c r="E35" s="11">
-        <v>707293.5</v>
+        <v>707453.6</v>
       </c>
       <c r="F35" s="11">
-        <v>770368.2</v>
+        <v>770369.6</v>
       </c>
       <c r="G35" s="11">
-        <v>705306.8</v>
+        <v>705319.8</v>
       </c>
       <c r="H35" s="11">
-        <v>727169.3</v>
+        <v>727526</v>
       </c>
       <c r="I35" s="11">
-        <v>666401.5</v>
+        <v>667336.6</v>
       </c>
       <c r="J35" s="11">
-        <v>706323.6</v>
+        <v>706902.2</v>
       </c>
       <c r="K35" s="11">
-        <v>697904.1</v>
+        <v>697993.9</v>
       </c>
       <c r="L35" s="11">
-        <v>678467.8</v>
+        <v>678743.9</v>
       </c>
       <c r="M35" s="11">
-        <v>737344</v>
+        <v>738762.6</v>
       </c>
       <c r="N35" s="11">
-        <v>746955.6</v>
+        <v>747699.8</v>
       </c>
       <c r="O35" s="11">
-        <v>0</v>
+        <v>788385.2</v>
       </c>
       <c r="P35" s="6"/>
       <c r="Q35" s="6">
-        <v>7924698.4999999981</v>
-      </c>
-    </row>
-    <row r="36" spans="2:17" x14ac:dyDescent="0.25">
+        <v>8717983.7999999989</v>
+      </c>
+    </row>
+    <row r="36" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B36" s="73" t="s">
         <v>40</v>
       </c>
       <c r="C36" s="13"/>
       <c r="D36" s="11">
-        <v>24215.3</v>
+        <v>24213.8</v>
       </c>
       <c r="E36" s="11">
-        <v>21125.200000000001</v>
+        <v>21117.9</v>
       </c>
       <c r="F36" s="11">
-        <v>23207</v>
+        <v>23191.7</v>
       </c>
       <c r="G36" s="11">
-        <v>20143.2</v>
+        <v>20124.2</v>
       </c>
       <c r="H36" s="11">
-        <v>18998</v>
+        <v>18976.400000000001</v>
       </c>
       <c r="I36" s="11">
-        <v>17369.8</v>
+        <v>17354.2</v>
       </c>
       <c r="J36" s="11">
-        <v>15759</v>
+        <v>15749.3</v>
       </c>
       <c r="K36" s="11">
-        <v>15589.8</v>
+        <v>15584.6</v>
       </c>
       <c r="L36" s="11">
-        <v>15385.3</v>
+        <v>15192.6</v>
       </c>
       <c r="M36" s="11">
-        <v>18768.400000000001</v>
+        <v>18083.099999999999</v>
       </c>
       <c r="N36" s="11">
-        <v>18766</v>
+        <v>18684.900000000001</v>
       </c>
       <c r="O36" s="11">
-        <v>0</v>
+        <v>18584.3</v>
       </c>
       <c r="P36" s="6"/>
       <c r="Q36" s="6">
-        <v>209326.99999999997</v>
-      </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.25">
+        <v>226857</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B37" s="73" t="s">
         <v>33</v>
       </c>
@@ -5258,66 +5255,66 @@
         <v>814116.3</v>
       </c>
       <c r="M37" s="9">
-        <v>844421.1</v>
+        <v>841991.8</v>
       </c>
       <c r="N37" s="9">
-        <v>841581.4</v>
+        <v>842049.5</v>
       </c>
       <c r="O37" s="9">
-        <v>0</v>
+        <v>863154.4</v>
       </c>
       <c r="P37" s="6"/>
       <c r="Q37" s="7">
-        <v>8861577.6999999993</v>
-      </c>
-    </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.25">
+        <v>9722770.9000000004</v>
+      </c>
+    </row>
+    <row r="38" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B38" s="74" t="s">
         <v>130</v>
       </c>
       <c r="C38" s="14"/>
       <c r="D38" s="11">
-        <v>1736819.9</v>
+        <v>1737169.8</v>
       </c>
       <c r="E38" s="11">
-        <v>1550058.2</v>
+        <v>1550257.9</v>
       </c>
       <c r="F38" s="11">
-        <v>1723023.5999999999</v>
+        <v>1723064.1999999997</v>
       </c>
       <c r="G38" s="11">
-        <v>1619586.5</v>
+        <v>1619651.1</v>
       </c>
       <c r="H38" s="11">
-        <v>1640078</v>
+        <v>1640458.9</v>
       </c>
       <c r="I38" s="11">
-        <v>1518150.6</v>
+        <v>1519108</v>
       </c>
       <c r="J38" s="11">
-        <v>1620137.7999999998</v>
+        <v>1620757</v>
       </c>
       <c r="K38" s="11">
-        <v>1628657.3</v>
+        <v>1628776.4</v>
       </c>
       <c r="L38" s="11">
-        <v>1601114.7000000002</v>
+        <v>1601241.5</v>
       </c>
       <c r="M38" s="11">
-        <v>1692877.9</v>
+        <v>1691735.5</v>
       </c>
       <c r="N38" s="11">
-        <v>1696550.9</v>
+        <v>1697547.4</v>
       </c>
       <c r="O38" s="11">
-        <v>0</v>
+        <v>1765465.9</v>
       </c>
       <c r="P38" s="6"/>
       <c r="Q38" s="11">
-        <v>18027055.399999999</v>
-      </c>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.25">
+        <v>19795233.600000001</v>
+      </c>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B39" s="74"/>
       <c r="C39" s="14"/>
       <c r="D39" s="11"/>
@@ -5335,7 +5332,7 @@
       <c r="P39" s="6"/>
       <c r="Q39" s="11"/>
     </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B40" s="71" t="s">
         <v>57</v>
       </c>
@@ -5354,53 +5351,53 @@
       <c r="P40" s="6"/>
       <c r="Q40" s="6"/>
     </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B41" s="73" t="s">
         <v>38</v>
       </c>
       <c r="C41" s="13"/>
       <c r="D41" s="11">
-        <v>4232.5</v>
+        <v>4230.6000000000004</v>
       </c>
       <c r="E41" s="11">
-        <v>3402.5</v>
+        <v>3404.3</v>
       </c>
       <c r="F41" s="11">
-        <v>3635.6</v>
+        <v>3647.7</v>
       </c>
       <c r="G41" s="11">
-        <v>3557.2</v>
+        <v>3567.3</v>
       </c>
       <c r="H41" s="11">
-        <v>3982.6</v>
+        <v>3988.6</v>
       </c>
       <c r="I41" s="11">
-        <v>3614.6</v>
+        <v>3622.9</v>
       </c>
       <c r="J41" s="11">
-        <v>3639.2</v>
+        <v>3648.2</v>
       </c>
       <c r="K41" s="11">
-        <v>3443.6</v>
+        <v>3445.6</v>
       </c>
       <c r="L41" s="11">
-        <v>4169.1000000000004</v>
+        <v>4169.5</v>
       </c>
       <c r="M41" s="11">
-        <v>3917.4</v>
+        <v>3976.1</v>
       </c>
       <c r="N41" s="11">
-        <v>2939.9</v>
+        <v>3028.9</v>
       </c>
       <c r="O41" s="11">
-        <v>0</v>
+        <v>3301.3</v>
       </c>
       <c r="P41" s="6"/>
       <c r="Q41" s="6">
-        <v>40534.199999999997</v>
-      </c>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.25">
+        <v>44031</v>
+      </c>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B42" s="73" t="s">
         <v>39</v>
       </c>
@@ -5424,29 +5421,29 @@
         <v>164455.79999999999</v>
       </c>
       <c r="J42" s="11">
-        <v>168798.4</v>
+        <v>168921.3</v>
       </c>
       <c r="K42" s="11">
-        <v>163098.1</v>
+        <v>163097.60000000001</v>
       </c>
       <c r="L42" s="11">
-        <v>150855.79999999999</v>
+        <v>150855.4</v>
       </c>
       <c r="M42" s="11">
-        <v>162873.29999999999</v>
+        <v>164447.4</v>
       </c>
       <c r="N42" s="11">
-        <v>167297.4</v>
+        <v>170913.1</v>
       </c>
       <c r="O42" s="11">
-        <v>0</v>
+        <v>176958.5</v>
       </c>
       <c r="P42" s="6"/>
       <c r="Q42" s="6">
-        <v>1841074.1</v>
-      </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.25">
+        <v>2023344.4000000001</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B43" s="73" t="s">
         <v>40</v>
       </c>
@@ -5455,44 +5452,44 @@
         <v>900.3</v>
       </c>
       <c r="E43" s="11">
-        <v>830.6</v>
+        <v>831.3</v>
       </c>
       <c r="F43" s="11">
-        <v>915.8</v>
+        <v>916.6</v>
       </c>
       <c r="G43" s="11">
-        <v>871</v>
+        <v>871.8</v>
       </c>
       <c r="H43" s="11">
-        <v>884.6</v>
+        <v>885.3</v>
       </c>
       <c r="I43" s="11">
-        <v>868.1</v>
+        <v>868.8</v>
       </c>
       <c r="J43" s="11">
-        <v>879.5</v>
+        <v>881.5</v>
       </c>
       <c r="K43" s="11">
-        <v>864</v>
+        <v>864.9</v>
       </c>
       <c r="L43" s="11">
-        <v>802</v>
+        <v>802.8</v>
       </c>
       <c r="M43" s="11">
-        <v>939.8</v>
+        <v>940.9</v>
       </c>
       <c r="N43" s="11">
-        <v>889.2</v>
+        <v>890.5</v>
       </c>
       <c r="O43" s="11">
-        <v>0</v>
+        <v>841.9</v>
       </c>
       <c r="P43" s="6"/>
       <c r="Q43" s="6">
-        <v>9644.9000000000015</v>
-      </c>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.25">
+        <v>10496.6</v>
+      </c>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B44" s="73" t="s">
         <v>33</v>
       </c>
@@ -5531,14 +5528,14 @@
         <v>334024.5</v>
       </c>
       <c r="O44" s="11">
-        <v>0</v>
+        <v>332445.90000000002</v>
       </c>
       <c r="P44" s="6"/>
       <c r="Q44" s="6">
-        <v>3540338.8000000003</v>
-      </c>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.25">
+        <v>3872784.7</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B45" s="73" t="s">
         <v>54</v>
       </c>
@@ -5577,63 +5574,63 @@
         <v>2059.5</v>
       </c>
       <c r="O45" s="9">
-        <v>0</v>
+        <v>2750</v>
       </c>
       <c r="P45" s="6"/>
       <c r="Q45" s="7">
-        <v>17942.099999999999</v>
-      </c>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.25">
+        <v>20692.099999999999</v>
+      </c>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B46" s="74" t="s">
         <v>58</v>
       </c>
       <c r="C46" s="14"/>
       <c r="D46" s="11">
-        <v>497233.3</v>
+        <v>497231.4</v>
       </c>
       <c r="E46" s="11">
-        <v>471296.5</v>
+        <v>471299</v>
       </c>
       <c r="F46" s="11">
-        <v>535860.5</v>
+        <v>535873.40000000014</v>
       </c>
       <c r="G46" s="11">
-        <v>496751.7</v>
+        <v>496762.60000000003</v>
       </c>
       <c r="H46" s="11">
-        <v>502151.10000000003</v>
+        <v>502157.80000000005</v>
       </c>
       <c r="I46" s="11">
-        <v>488391.3</v>
+        <v>488400.29999999993</v>
       </c>
       <c r="J46" s="11">
-        <v>492040.70000000007</v>
+        <v>492174.60000000003</v>
       </c>
       <c r="K46" s="11">
-        <v>504467.80000000005</v>
+        <v>504470.20000000007</v>
       </c>
       <c r="L46" s="11">
-        <v>458922.4</v>
+        <v>458923.19999999995</v>
       </c>
       <c r="M46" s="11">
-        <v>495208.3</v>
+        <v>496842.2</v>
       </c>
       <c r="N46" s="11">
-        <v>507210.5</v>
+        <v>510916.5</v>
       </c>
       <c r="O46" s="11">
-        <v>0</v>
+        <v>516297.6</v>
       </c>
       <c r="P46" s="6"/>
       <c r="Q46" s="11">
-        <v>5449534.0999999996</v>
-      </c>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.25">
+        <v>5971348.7999999998</v>
+      </c>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B47" s="74"/>
     </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B48" s="71" t="s">
         <v>169</v>
       </c>
@@ -5672,60 +5669,60 @@
         <v>564451.5</v>
       </c>
       <c r="O48" s="11">
-        <v>0</v>
+        <v>594233.30000000005</v>
       </c>
       <c r="P48" s="6"/>
       <c r="Q48" s="63">
-        <v>564451.5</v>
-      </c>
-    </row>
-    <row r="49" spans="2:17" x14ac:dyDescent="0.25">
+        <v>594233.30000000005</v>
+      </c>
+    </row>
+    <row r="49" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B49" s="71" t="s">
         <v>167</v>
       </c>
       <c r="C49" s="13"/>
       <c r="D49" s="11">
-        <v>-101444.5</v>
+        <v>-101756.4</v>
       </c>
       <c r="E49" s="11">
-        <v>-116029.3</v>
+        <v>-116181.7</v>
       </c>
       <c r="F49" s="11">
-        <v>-116727.1</v>
+        <v>-116720.7</v>
       </c>
       <c r="G49" s="11">
-        <v>-85742.9</v>
+        <v>-85741.8</v>
       </c>
       <c r="H49" s="11">
-        <v>-98528.6</v>
+        <v>-98826.6</v>
       </c>
       <c r="I49" s="11">
-        <v>-103353.4</v>
+        <v>-104283.3</v>
       </c>
       <c r="J49" s="11">
-        <v>-115364.9</v>
+        <v>-116076.1</v>
       </c>
       <c r="K49" s="11">
-        <v>-113025.9</v>
+        <v>-113115.6</v>
       </c>
       <c r="L49" s="11">
-        <v>-117364.3</v>
+        <v>-117700</v>
       </c>
       <c r="M49" s="11">
-        <v>-120127.6</v>
+        <v>-120045.6</v>
       </c>
       <c r="N49" s="11">
-        <v>-118613.6</v>
+        <v>-124140.1</v>
       </c>
       <c r="O49" s="11">
-        <v>0</v>
+        <v>-129587.5</v>
       </c>
       <c r="P49" s="6"/>
       <c r="Q49" s="6">
-        <v>-1206322.1000000003</v>
-      </c>
-    </row>
-    <row r="50" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>-1344175.4000000001</v>
+      </c>
+    </row>
+    <row r="50" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B50" s="71"/>
       <c r="D50" s="19"/>
       <c r="E50" s="19"/>
@@ -5742,54 +5739,54 @@
       <c r="P50" s="6"/>
       <c r="Q50" s="8"/>
     </row>
-    <row r="51" spans="2:17" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:17" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B51" s="86" t="s">
         <v>200</v>
       </c>
       <c r="D51" s="11">
-        <v>17013506.299999997</v>
+        <v>17012904.699999999</v>
       </c>
       <c r="E51" s="11">
-        <v>15654379.699999999</v>
+        <v>15654097.000000004</v>
       </c>
       <c r="F51" s="11">
-        <v>16084400</v>
+        <v>16084435.800000003</v>
       </c>
       <c r="G51" s="11">
-        <v>14141811.800000001</v>
+        <v>14141831.6</v>
       </c>
       <c r="H51" s="11">
-        <v>13702322.699999999</v>
+        <v>13701743.799999997</v>
       </c>
       <c r="I51" s="11">
-        <v>13479632.199999997</v>
+        <v>13477788.599999996</v>
       </c>
       <c r="J51" s="11">
-        <v>14003902.799999999</v>
+        <v>14002557.199999999</v>
       </c>
       <c r="K51" s="11">
-        <v>13723239.999999998</v>
+        <v>13723103.200000003</v>
       </c>
       <c r="L51" s="11">
-        <v>12917857.800000003</v>
+        <v>12917292.700000003</v>
       </c>
       <c r="M51" s="11">
-        <v>14448741.699999999</v>
+        <v>14448439.299999999</v>
       </c>
       <c r="N51" s="11">
-        <v>15443151.300000001</v>
+        <v>15433483.599999998</v>
       </c>
       <c r="O51" s="11">
-        <v>0</v>
+        <v>17464973.899999999</v>
       </c>
       <c r="P51" s="6"/>
       <c r="Q51" s="6">
-        <v>160612946.30000001</v>
-      </c>
-    </row>
-    <row r="52" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>178062651.40000001</v>
+      </c>
+    </row>
+    <row r="52" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B52" s="93" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C52" s="20"/>
       <c r="D52" s="2"/>
@@ -5809,7 +5806,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="53" spans="2:17" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:17" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B53" s="69"/>
       <c r="C53" s="4"/>
       <c r="D53" s="3" t="s">
@@ -5850,10 +5847,10 @@
       </c>
       <c r="P53" s="3"/>
       <c r="Q53" s="3" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="54" spans="2:17" x14ac:dyDescent="0.25">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="54" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B54" s="72" t="s">
         <v>37</v>
       </c>
@@ -5873,7 +5870,7 @@
       <c r="P54" s="6"/>
       <c r="Q54" s="6"/>
     </row>
-    <row r="55" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B55" s="71" t="s">
         <v>34</v>
       </c>
@@ -5892,7 +5889,7 @@
       <c r="P55" s="6"/>
       <c r="Q55" s="6"/>
     </row>
-    <row r="56" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B56" s="73" t="s">
         <v>26</v>
       </c>
@@ -5931,14 +5928,14 @@
         <v>511516.5</v>
       </c>
       <c r="O56" s="11">
-        <v>0</v>
+        <v>827343.9</v>
       </c>
       <c r="P56" s="6"/>
       <c r="Q56" s="6">
-        <v>3798917.6000000006</v>
-      </c>
-    </row>
-    <row r="57" spans="2:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>4626261.5000000009</v>
+      </c>
+    </row>
+    <row r="57" spans="2:17" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B57" s="73" t="s">
         <v>27</v>
       </c>
@@ -5965,26 +5962,26 @@
         <v>95729.8</v>
       </c>
       <c r="K57" s="11">
-        <v>79375.399999999994</v>
+        <v>79402.5</v>
       </c>
       <c r="L57" s="11">
-        <v>117466.4</v>
+        <v>117548.3</v>
       </c>
       <c r="M57" s="11">
-        <v>250068.6</v>
+        <v>250227.4</v>
       </c>
       <c r="N57" s="11">
-        <v>350411.9</v>
+        <v>351252</v>
       </c>
       <c r="O57" s="11">
-        <v>0</v>
+        <v>546788.4</v>
       </c>
       <c r="P57" s="6"/>
       <c r="Q57" s="6">
-        <v>2868652.6</v>
-      </c>
-    </row>
-    <row r="58" spans="2:17" x14ac:dyDescent="0.25">
+        <v>3416548.9</v>
+      </c>
+    </row>
+    <row r="58" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B58" s="73" t="s">
         <v>59</v>
       </c>
@@ -6023,14 +6020,14 @@
         <v>1199049.5</v>
       </c>
       <c r="O58" s="11">
-        <v>0</v>
+        <v>1327947.7</v>
       </c>
       <c r="P58" s="6"/>
       <c r="Q58" s="6">
-        <v>13076908.699999999</v>
-      </c>
-    </row>
-    <row r="59" spans="2:17" x14ac:dyDescent="0.25">
+        <v>14404856.399999999</v>
+      </c>
+    </row>
+    <row r="59" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B59" s="73"/>
       <c r="C59" s="15"/>
       <c r="D59" s="11"/>
@@ -6048,7 +6045,7 @@
       <c r="P59" s="6"/>
       <c r="Q59" s="6"/>
     </row>
-    <row r="60" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B60" s="73" t="s">
         <v>53</v>
       </c>
@@ -6078,23 +6075,23 @@
         <v>10734.7</v>
       </c>
       <c r="L60" s="11">
-        <v>3810.2</v>
+        <v>3818.5</v>
       </c>
       <c r="M60" s="11">
-        <v>6915.6</v>
+        <v>7055.5</v>
       </c>
       <c r="N60" s="11">
-        <v>8890.7000000000007</v>
+        <v>8925.4</v>
       </c>
       <c r="O60" s="11">
-        <v>0</v>
+        <v>9619.7000000000007</v>
       </c>
       <c r="P60" s="6"/>
       <c r="Q60" s="6">
-        <v>107722.29999999999</v>
-      </c>
-    </row>
-    <row r="61" spans="2:17" x14ac:dyDescent="0.25">
+        <v>117524.89999999998</v>
+      </c>
+    </row>
+    <row r="61" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B61" s="73" t="s">
         <v>71</v>
       </c>
@@ -6133,14 +6130,14 @@
         <v>262471.2</v>
       </c>
       <c r="O61" s="11">
-        <v>0</v>
+        <v>252559.6</v>
       </c>
       <c r="P61" s="6"/>
       <c r="Q61" s="6">
-        <v>2529350.7000000002</v>
-      </c>
-    </row>
-    <row r="62" spans="2:17" x14ac:dyDescent="0.25">
+        <v>2781910.3000000003</v>
+      </c>
+    </row>
+    <row r="62" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B62" s="73"/>
       <c r="C62" s="13"/>
       <c r="D62" s="11"/>
@@ -6158,7 +6155,7 @@
       <c r="P62" s="6"/>
       <c r="Q62" s="6"/>
     </row>
-    <row r="63" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B63" s="73" t="s">
         <v>72</v>
       </c>
@@ -6178,7 +6175,7 @@
       <c r="P63" s="6"/>
       <c r="Q63" s="6"/>
     </row>
-    <row r="64" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B64" s="76" t="s">
         <v>41</v>
       </c>
@@ -6217,14 +6214,14 @@
         <v>86521.8</v>
       </c>
       <c r="O64" s="11">
-        <v>0</v>
+        <v>78374.5</v>
       </c>
       <c r="P64" s="6"/>
       <c r="Q64" s="6">
-        <v>1129566.7</v>
-      </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.25">
+        <v>1207941.2</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B65" s="76" t="s">
         <v>42</v>
       </c>
@@ -6270,7 +6267,7 @@
         <v>2348.5</v>
       </c>
     </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B66" s="76" t="s">
         <v>44</v>
       </c>
@@ -6309,14 +6306,14 @@
         <v>45059.1</v>
       </c>
       <c r="O66" s="11">
-        <v>0</v>
+        <v>51788.6</v>
       </c>
       <c r="P66" s="6"/>
       <c r="Q66" s="6">
-        <v>527361.10000000009</v>
-      </c>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.25">
+        <v>579149.70000000007</v>
+      </c>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B67" s="76" t="s">
         <v>43</v>
       </c>
@@ -6340,7 +6337,7 @@
         <v>215926.6</v>
       </c>
       <c r="J67" s="9">
-        <v>201170.2</v>
+        <v>201171.3</v>
       </c>
       <c r="K67" s="9">
         <v>206830.4</v>
@@ -6355,14 +6352,14 @@
         <v>252749.1</v>
       </c>
       <c r="O67" s="9">
-        <v>0</v>
+        <v>256938.5</v>
       </c>
       <c r="P67" s="6"/>
       <c r="Q67" s="7">
-        <v>2588381.5</v>
-      </c>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.25">
+        <v>2845321.1</v>
+      </c>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B68" s="73" t="s">
         <v>52</v>
       </c>
@@ -6386,7 +6383,7 @@
         <v>387904.7</v>
       </c>
       <c r="J68" s="11">
-        <v>377235.6</v>
+        <v>377236.69999999995</v>
       </c>
       <c r="K68" s="11">
         <v>381664.6</v>
@@ -6401,14 +6398,14 @@
         <v>384330</v>
       </c>
       <c r="O68" s="11">
-        <v>0</v>
+        <v>387101.6</v>
       </c>
       <c r="P68" s="6"/>
       <c r="Q68" s="11">
-        <v>4247657.8</v>
-      </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.25">
+        <v>4634760.5</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B69" s="77"/>
       <c r="C69" s="13"/>
       <c r="D69" s="11"/>
@@ -6426,7 +6423,7 @@
       <c r="P69" s="6"/>
       <c r="Q69" s="11"/>
     </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B70" s="73" t="s">
         <v>62</v>
       </c>
@@ -6446,7 +6443,7 @@
       <c r="P70" s="6"/>
       <c r="Q70" s="6"/>
     </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B71" s="76" t="s">
         <v>61</v>
       </c>
@@ -6479,20 +6476,20 @@
         <v>256238.2</v>
       </c>
       <c r="M71" s="11">
-        <v>280520.8</v>
+        <v>281010.59999999998</v>
       </c>
       <c r="N71" s="11">
-        <v>281042.59999999998</v>
+        <v>283539.20000000001</v>
       </c>
       <c r="O71" s="11">
-        <v>0</v>
+        <v>289074.90000000002</v>
       </c>
       <c r="P71" s="6"/>
       <c r="Q71" s="6">
-        <v>3016581.9000000004</v>
-      </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.25">
+        <v>3308643.2000000007</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B72" s="76" t="s">
         <v>38</v>
       </c>
@@ -6531,14 +6528,14 @@
         <v>6438.6</v>
       </c>
       <c r="O72" s="11">
-        <v>0</v>
+        <v>7238.9</v>
       </c>
       <c r="P72" s="6"/>
       <c r="Q72" s="6">
-        <v>73944</v>
-      </c>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.25">
+        <v>81182.899999999994</v>
+      </c>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B73" s="76" t="s">
         <v>39</v>
       </c>
@@ -6571,20 +6568,20 @@
         <v>1596965.7</v>
       </c>
       <c r="M73" s="11">
-        <v>1704595.3</v>
+        <v>1704451.9</v>
       </c>
       <c r="N73" s="11">
         <v>1755517.4</v>
       </c>
       <c r="O73" s="11">
-        <v>0</v>
+        <v>1853948.2</v>
       </c>
       <c r="P73" s="6"/>
       <c r="Q73" s="6">
-        <v>18456099.800000001</v>
-      </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.25">
+        <v>20309904.599999998</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B74" s="76" t="s">
         <v>40</v>
       </c>
@@ -6620,17 +6617,17 @@
         <v>57.3</v>
       </c>
       <c r="N74" s="9">
-        <v>80.900000000000006</v>
+        <v>80.7</v>
       </c>
       <c r="O74" s="9">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="P74" s="6"/>
       <c r="Q74" s="7">
-        <v>1265.3999999999999</v>
-      </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.25">
+        <v>1347.1999999999998</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B75" s="73" t="s">
         <v>63</v>
       </c>
@@ -6663,20 +6660,20 @@
         <v>1859229.6</v>
       </c>
       <c r="M75" s="11">
-        <v>1990806</v>
+        <v>1991152.4</v>
       </c>
       <c r="N75" s="11">
-        <v>2043079.4999999998</v>
+        <v>2045575.9</v>
       </c>
       <c r="O75" s="11">
-        <v>0</v>
+        <v>2150344</v>
       </c>
       <c r="P75" s="6"/>
       <c r="Q75" s="11">
-        <v>21547891.100000001</v>
-      </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.25">
+        <v>23701077.899999999</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B76" s="77"/>
       <c r="C76" s="13"/>
       <c r="D76" s="11"/>
@@ -6694,7 +6691,7 @@
       <c r="P76" s="6"/>
       <c r="Q76" s="11"/>
     </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B77" s="73" t="s">
         <v>64</v>
       </c>
@@ -6714,7 +6711,7 @@
       <c r="P77" s="6"/>
       <c r="Q77" s="6"/>
     </row>
-    <row r="78" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B78" s="76" t="s">
         <v>38</v>
       </c>
@@ -6753,14 +6750,14 @@
         <v>48888.4</v>
       </c>
       <c r="O78" s="11">
-        <v>0</v>
+        <v>49307.5</v>
       </c>
       <c r="P78" s="6"/>
       <c r="Q78" s="6">
-        <v>667510.00000000012</v>
-      </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.25">
+        <v>716817.50000000012</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B79" s="76" t="s">
         <v>39</v>
       </c>
@@ -6799,14 +6796,14 @@
         <v>964129.5</v>
       </c>
       <c r="O79" s="11">
-        <v>0</v>
+        <v>1100422.3999999999</v>
       </c>
       <c r="P79" s="6"/>
       <c r="Q79" s="6">
-        <v>9709478.5</v>
-      </c>
-    </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.25">
+        <v>10809900.9</v>
+      </c>
+    </row>
+    <row r="80" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B80" s="76" t="s">
         <v>66</v>
       </c>
@@ -6845,14 +6842,14 @@
         <v>77801.2</v>
       </c>
       <c r="O80" s="9">
-        <v>0</v>
+        <v>87237.3</v>
       </c>
       <c r="P80" s="6"/>
       <c r="Q80" s="7">
-        <v>802243.9</v>
-      </c>
-    </row>
-    <row r="81" spans="2:17" x14ac:dyDescent="0.25">
+        <v>889481.20000000007</v>
+      </c>
+    </row>
+    <row r="81" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B81" s="73" t="s">
         <v>65</v>
       </c>
@@ -6891,14 +6888,14 @@
         <v>1090819.1000000001</v>
       </c>
       <c r="O81" s="23">
-        <v>0</v>
+        <v>1236967.2</v>
       </c>
       <c r="P81" s="6"/>
       <c r="Q81" s="23">
-        <v>11179232.4</v>
-      </c>
-    </row>
-    <row r="82" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>12416199.6</v>
+      </c>
+    </row>
+    <row r="82" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B82" s="77"/>
       <c r="C82" s="13"/>
       <c r="D82" s="19"/>
@@ -6916,7 +6913,7 @@
       <c r="P82" s="8"/>
       <c r="Q82" s="19"/>
     </row>
-    <row r="83" spans="2:17" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:17" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B83" s="74" t="s">
         <v>35</v>
       </c>
@@ -6940,29 +6937,29 @@
         <v>4753257.0999999996</v>
       </c>
       <c r="J83" s="11">
-        <v>5059420.5</v>
+        <v>5059421.5999999996</v>
       </c>
       <c r="K83" s="11">
-        <v>5014288.3</v>
+        <v>5014315.3999999994</v>
       </c>
       <c r="L83" s="11">
-        <v>4758807.9000000004</v>
+        <v>4758898.0999999996</v>
       </c>
       <c r="M83" s="11">
-        <v>5419482.4000000004</v>
+        <v>5420127.5</v>
       </c>
       <c r="N83" s="11">
-        <v>5850568.4000000004</v>
+        <v>5853939.5999999996</v>
       </c>
       <c r="O83" s="11">
-        <v>0</v>
+        <v>6738672.1000000006</v>
       </c>
       <c r="P83" s="6"/>
       <c r="Q83" s="11">
-        <v>59356333.199999996</v>
-      </c>
-    </row>
-    <row r="84" spans="2:17" x14ac:dyDescent="0.25">
+        <v>66099140</v>
+      </c>
+    </row>
+    <row r="84" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B84" s="78"/>
       <c r="C84" s="14"/>
       <c r="D84" s="11"/>
@@ -6980,7 +6977,7 @@
       <c r="P84" s="6"/>
       <c r="Q84" s="11"/>
     </row>
-    <row r="85" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B85" s="71" t="s">
         <v>171</v>
       </c>
@@ -6999,7 +6996,7 @@
       <c r="P85" s="6"/>
       <c r="Q85" s="6"/>
     </row>
-    <row r="86" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B86" s="73" t="s">
         <v>5</v>
       </c>
@@ -7032,20 +7029,20 @@
         <v>662679.05000000005</v>
       </c>
       <c r="M86" s="65">
-        <v>722643.06</v>
+        <v>722582.35</v>
       </c>
       <c r="N86" s="11">
-        <v>991467.4</v>
+        <v>704391.52</v>
       </c>
       <c r="O86" s="11">
-        <v>0</v>
+        <v>1484413.54</v>
       </c>
       <c r="P86" s="6"/>
       <c r="Q86" s="97">
-        <v>8694801.2100000009</v>
-      </c>
-    </row>
-    <row r="87" spans="2:17" x14ac:dyDescent="0.25">
+        <v>9892078.1600000001</v>
+      </c>
+    </row>
+    <row r="87" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B87" s="73" t="s">
         <v>0</v>
       </c>
@@ -7078,20 +7075,20 @@
         <v>1338132.56</v>
       </c>
       <c r="M87" s="65">
-        <v>1530956.03</v>
+        <v>1530824.75</v>
       </c>
       <c r="N87" s="11">
-        <v>2071075.56</v>
+        <v>1697693.26</v>
       </c>
       <c r="O87" s="11">
-        <v>0</v>
+        <v>2101682.9300000002</v>
       </c>
       <c r="P87" s="6"/>
       <c r="Q87" s="97">
-        <v>17922138.330000002</v>
-      </c>
-    </row>
-    <row r="88" spans="2:17" x14ac:dyDescent="0.25">
+        <v>19650307.680000003</v>
+      </c>
+    </row>
+    <row r="88" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B88" s="73" t="s">
         <v>1</v>
       </c>
@@ -7124,20 +7121,20 @@
         <v>421029.77</v>
       </c>
       <c r="M88" s="65">
-        <v>603717.19999999995</v>
+        <v>603665.09</v>
       </c>
       <c r="N88" s="11">
-        <v>523351.19</v>
+        <v>574075.61</v>
       </c>
       <c r="O88" s="11">
-        <v>0</v>
+        <v>611048.79</v>
       </c>
       <c r="P88" s="6"/>
       <c r="Q88" s="97">
-        <v>5717968.7200000007</v>
-      </c>
-    </row>
-    <row r="89" spans="2:17" x14ac:dyDescent="0.25">
+        <v>6379689.8200000003</v>
+      </c>
+    </row>
+    <row r="89" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B89" s="73" t="s">
         <v>2</v>
       </c>
@@ -7170,20 +7167,20 @@
         <v>1345306.55</v>
       </c>
       <c r="M89" s="65">
-        <v>1347203.64</v>
+        <v>1347087.3600000001</v>
       </c>
       <c r="N89" s="11">
-        <v>1396256.37</v>
+        <v>1246133.8700000001</v>
       </c>
       <c r="O89" s="11">
-        <v>0</v>
+        <v>1999052.35</v>
       </c>
       <c r="P89" s="6"/>
       <c r="Q89" s="97">
-        <v>14403303.350000001</v>
-      </c>
-    </row>
-    <row r="90" spans="2:17" x14ac:dyDescent="0.25">
+        <v>16252116.92</v>
+      </c>
+    </row>
+    <row r="90" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B90" s="73" t="s">
         <v>3</v>
       </c>
@@ -7216,20 +7213,20 @@
         <v>17978.96</v>
       </c>
       <c r="M90" s="65">
-        <v>24487.55</v>
+        <v>24485.439999999999</v>
       </c>
       <c r="N90" s="11">
-        <v>9174.5</v>
+        <v>18643.29</v>
       </c>
       <c r="O90" s="11">
-        <v>0</v>
+        <v>28723.53</v>
       </c>
       <c r="P90" s="6"/>
       <c r="Q90" s="97">
-        <v>229817.24</v>
-      </c>
-    </row>
-    <row r="91" spans="2:17" x14ac:dyDescent="0.25">
+        <v>268007.45</v>
+      </c>
+    </row>
+    <row r="91" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B91" s="73" t="s">
         <v>4</v>
       </c>
@@ -7275,7 +7272,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B92" s="73" t="s">
         <v>55</v>
       </c>
@@ -7321,7 +7318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B93" s="74" t="s">
         <v>172</v>
       </c>
@@ -7354,20 +7351,20 @@
         <v>3785126.8899999997</v>
       </c>
       <c r="M93" s="65">
-        <v>4229007.4799999995</v>
+        <v>4228644.99</v>
       </c>
       <c r="N93" s="11">
-        <v>4991325.0199999996</v>
+        <v>4240937.55</v>
       </c>
       <c r="O93" s="11">
-        <v>0</v>
+        <v>6224921.1399999997</v>
       </c>
       <c r="P93" s="6"/>
       <c r="Q93" s="65">
-        <v>46968028.850000009</v>
-      </c>
-    </row>
-    <row r="94" spans="2:17" x14ac:dyDescent="0.25">
+        <v>52442200.030000009</v>
+      </c>
+    </row>
+    <row r="94" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B94" s="78"/>
       <c r="C94" s="14"/>
       <c r="D94" s="11"/>
@@ -7385,7 +7382,7 @@
       <c r="P94" s="6"/>
       <c r="Q94" s="65"/>
     </row>
-    <row r="95" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B95" s="79" t="s">
         <v>173</v>
       </c>
@@ -7405,7 +7402,7 @@
       <c r="P95" s="6"/>
       <c r="Q95" s="97"/>
     </row>
-    <row r="96" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B96" s="80" t="s">
         <v>28</v>
       </c>
@@ -7438,20 +7435,20 @@
         <v>51708.160000000003</v>
       </c>
       <c r="M96" s="65">
-        <v>55489.27</v>
+        <v>55484.480000000003</v>
       </c>
       <c r="N96" s="11">
-        <v>81485.399999999994</v>
+        <v>65875.67</v>
       </c>
       <c r="O96" s="11">
-        <v>0</v>
+        <v>136635.78</v>
       </c>
       <c r="P96" s="6"/>
       <c r="Q96" s="97">
-        <v>604886.17000000016</v>
-      </c>
-    </row>
-    <row r="97" spans="2:17" x14ac:dyDescent="0.25">
+        <v>725907.43000000017</v>
+      </c>
+    </row>
+    <row r="97" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B97" s="80" t="s">
         <v>29</v>
       </c>
@@ -7484,20 +7481,20 @@
         <v>2050190.77</v>
       </c>
       <c r="M97" s="65">
-        <v>2114519.87</v>
+        <v>2114337.36</v>
       </c>
       <c r="N97" s="11">
-        <v>1449408.53</v>
+        <v>2241742.4300000002</v>
       </c>
       <c r="O97" s="11">
-        <v>0</v>
+        <v>1740655.64</v>
       </c>
       <c r="P97" s="6"/>
       <c r="Q97" s="97">
-        <v>22965298.420000002</v>
-      </c>
-    </row>
-    <row r="98" spans="2:17" x14ac:dyDescent="0.25">
+        <v>25498105.449999999</v>
+      </c>
+    </row>
+    <row r="98" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B98" s="80" t="s">
         <v>30</v>
       </c>
@@ -7530,20 +7527,20 @@
         <v>85101.92</v>
       </c>
       <c r="M98" s="65">
-        <v>116755.69</v>
+        <v>116745.62</v>
       </c>
       <c r="N98" s="11">
-        <v>160654.91</v>
+        <v>110238.6</v>
       </c>
       <c r="O98" s="11">
-        <v>0</v>
+        <v>237460.65</v>
       </c>
       <c r="P98" s="6"/>
       <c r="Q98" s="97">
-        <v>1338824.8599999999</v>
-      </c>
-    </row>
-    <row r="99" spans="2:17" x14ac:dyDescent="0.25">
+        <v>1525859.13</v>
+      </c>
+    </row>
+    <row r="99" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B99" s="80" t="s">
         <v>31</v>
       </c>
@@ -7576,20 +7573,20 @@
         <v>355606.32</v>
       </c>
       <c r="M99" s="65">
-        <v>363041.82</v>
+        <v>363010.48</v>
       </c>
       <c r="N99" s="11">
-        <v>337124.29</v>
+        <v>368123.97</v>
       </c>
       <c r="O99" s="11">
-        <v>0</v>
+        <v>455088.16</v>
       </c>
       <c r="P99" s="6"/>
       <c r="Q99" s="97">
-        <v>4006485.34</v>
-      </c>
-    </row>
-    <row r="100" spans="2:17" x14ac:dyDescent="0.25">
+        <v>4492541.84</v>
+      </c>
+    </row>
+    <row r="100" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B100" s="80" t="s">
         <v>32</v>
       </c>
@@ -7622,20 +7619,20 @@
         <v>1156549.79</v>
       </c>
       <c r="M100" s="64">
-        <v>1075399.74</v>
+        <v>1075306.92</v>
       </c>
       <c r="N100" s="9">
-        <v>1101652.19</v>
+        <v>1102977.71</v>
       </c>
       <c r="O100" s="9">
-        <v>0</v>
+        <v>823046.68</v>
       </c>
       <c r="P100" s="6"/>
       <c r="Q100" s="98">
-        <v>12296836.77</v>
-      </c>
-    </row>
-    <row r="101" spans="2:17" x14ac:dyDescent="0.25">
+        <v>13121116.149999999</v>
+      </c>
+    </row>
+    <row r="101" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B101" s="81" t="s">
         <v>174</v>
       </c>
@@ -7668,20 +7665,20 @@
         <v>3699156.96</v>
       </c>
       <c r="M101" s="94">
-        <v>3725206.3899999997</v>
+        <v>3724884.86</v>
       </c>
       <c r="N101" s="23">
-        <v>3130325.32</v>
+        <v>3888958.38</v>
       </c>
       <c r="O101" s="23">
-        <v>0</v>
+        <v>3392886.91</v>
       </c>
       <c r="P101" s="6"/>
       <c r="Q101" s="94">
-        <v>41212331.559999995</v>
-      </c>
-    </row>
-    <row r="102" spans="2:17" x14ac:dyDescent="0.25">
+        <v>45363530</v>
+      </c>
+    </row>
+    <row r="102" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B102" s="82"/>
       <c r="C102" s="12"/>
       <c r="D102" s="11"/>
@@ -7699,7 +7696,7 @@
       <c r="P102" s="6"/>
       <c r="Q102" s="65"/>
     </row>
-    <row r="103" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B103" s="81" t="s">
         <v>170</v>
       </c>
@@ -7745,9 +7742,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B104" s="93" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C104" s="20"/>
       <c r="D104" s="2"/>
@@ -7767,7 +7764,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="105" spans="2:17" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:17" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B105" s="69"/>
       <c r="C105" s="4"/>
       <c r="D105" s="3" t="s">
@@ -7808,10 +7805,10 @@
       </c>
       <c r="P105" s="3"/>
       <c r="Q105" s="3" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="106" spans="2:17" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="106" spans="2:17" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B106" s="69"/>
       <c r="C106" s="4"/>
       <c r="D106" s="61"/>
@@ -7829,7 +7826,7 @@
       <c r="P106" s="61"/>
       <c r="Q106" s="61"/>
     </row>
-    <row r="107" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B107" s="79" t="s">
         <v>165</v>
       </c>
@@ -7862,20 +7859,20 @@
         <v>7484283.8499999996</v>
       </c>
       <c r="M107" s="65">
-        <v>7954213.8699999992</v>
+        <v>7953529.8499999996</v>
       </c>
       <c r="N107" s="11">
-        <v>8121650.3399999999</v>
+        <v>8129895.9299999997</v>
       </c>
       <c r="O107" s="11">
-        <v>0</v>
+        <v>9617808.0500000007</v>
       </c>
       <c r="P107" s="6"/>
       <c r="Q107" s="97">
-        <v>88180360.409999996</v>
-      </c>
-    </row>
-    <row r="108" spans="2:17" x14ac:dyDescent="0.25">
+        <v>97805730.029999986</v>
+      </c>
+    </row>
+    <row r="108" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B108" s="83" t="s">
         <v>201</v>
       </c>
@@ -7907,19 +7904,19 @@
         <v>249476.12833333333</v>
       </c>
       <c r="M108" s="65">
-        <v>256587.54419354835</v>
+        <v>256565.47903225807</v>
       </c>
       <c r="N108" s="11">
-        <v>270721.67800000001</v>
+        <v>270996.53100000002</v>
       </c>
       <c r="O108" s="11">
-        <v>0</v>
+        <v>310251.8725806452</v>
       </c>
       <c r="Q108" s="99">
-        <v>264279.90344930871</v>
-      </c>
-    </row>
-    <row r="109" spans="2:17" x14ac:dyDescent="0.25">
+        <v>268131.9665301459</v>
+      </c>
+    </row>
+    <row r="109" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B109" s="84"/>
       <c r="D109" s="11"/>
       <c r="E109" s="11"/>
@@ -7935,99 +7932,99 @@
       <c r="O109" s="11"/>
       <c r="Q109" s="65"/>
     </row>
-    <row r="110" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B110" s="79" t="s">
         <v>6</v>
       </c>
       <c r="C110" s="10"/>
       <c r="D110" s="11">
-        <v>1657986.3699999973</v>
+        <v>1657384.7699999996</v>
       </c>
       <c r="E110" s="11">
-        <v>1089157.7499999981</v>
+        <v>1088875.0500000026</v>
       </c>
       <c r="F110" s="11">
-        <v>1451142.7000000011</v>
+        <v>1451178.5000000037</v>
       </c>
       <c r="G110" s="11">
-        <v>1080583.0900000017</v>
+        <v>1080602.8899999987</v>
       </c>
       <c r="H110" s="11">
-        <v>1110101.42</v>
+        <v>1109522.5199999977</v>
       </c>
       <c r="I110" s="11">
-        <v>1385647.2599999979</v>
+        <v>1383803.6599999964</v>
       </c>
       <c r="J110" s="11">
-        <v>1161277.5899999989</v>
+        <v>1159930.8899999997</v>
       </c>
       <c r="K110" s="11">
-        <v>919612.46999999881</v>
+        <v>919448.57000000402</v>
       </c>
       <c r="L110" s="11">
-        <v>674766.05000000261</v>
+        <v>674110.75000000373</v>
       </c>
       <c r="M110" s="65">
-        <v>1075045.4299999997</v>
+        <v>1074781.9499999993</v>
       </c>
       <c r="N110" s="11">
-        <v>1470932.5600000005</v>
+        <v>1449648.0699999984</v>
       </c>
       <c r="O110" s="11">
-        <v>0</v>
+        <v>1108493.7499999963</v>
       </c>
       <c r="P110" s="6"/>
       <c r="Q110" s="65">
-        <v>13076252.690000027</v>
-      </c>
-    </row>
-    <row r="111" spans="2:17" x14ac:dyDescent="0.25">
+        <v>14157781.37000002</v>
+      </c>
+    </row>
+    <row r="111" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B111" s="85" t="s">
         <v>166</v>
       </c>
       <c r="C111" s="10"/>
       <c r="D111" s="21">
-        <v>9.7451186179065133E-2</v>
+        <v>9.7419270796244434E-2</v>
       </c>
       <c r="E111" s="21">
-        <v>6.957527355746955E-2</v>
+        <v>6.9558470859098567E-2</v>
       </c>
       <c r="F111" s="21">
-        <v>9.022050558304949E-2</v>
+        <v>9.022253052855006E-2</v>
       </c>
       <c r="G111" s="21">
-        <v>7.6410512689753213E-2</v>
+        <v>7.6411805808803343E-2</v>
       </c>
       <c r="H111" s="21">
-        <v>8.1015565339152315E-2</v>
+        <v>8.0976738157956071E-2</v>
       </c>
       <c r="I111" s="21">
-        <v>0.10279562820712558</v>
+        <v>0.10267290139867581</v>
       </c>
       <c r="J111" s="21">
-        <v>8.2925282086362309E-2</v>
+        <v>8.2837075645011457E-2</v>
       </c>
       <c r="K111" s="21">
-        <v>6.7011323127774414E-2</v>
+        <v>6.7000047773451407E-2</v>
       </c>
       <c r="L111" s="21">
-        <v>5.2235135302387554E-2</v>
+        <v>5.2186690017483585E-2</v>
       </c>
       <c r="M111" s="95">
-        <v>7.4404086689431215E-2</v>
+        <v>7.4387408057284041E-2</v>
       </c>
       <c r="N111" s="21">
-        <v>9.5248212714201697E-2</v>
-      </c>
-      <c r="O111" s="21" t="s">
-        <v>211</v>
+        <v>9.3928766024023155E-2</v>
+      </c>
+      <c r="O111" s="21">
+        <v>6.3469533727731273E-2</v>
       </c>
       <c r="P111" s="22"/>
       <c r="Q111" s="95">
-        <v>8.1414686619194571E-2</v>
-      </c>
-    </row>
-    <row r="112" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>7.9510112079573467E-2</v>
+      </c>
+    </row>
+    <row r="112" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B112" s="71"/>
       <c r="D112" s="8"/>
       <c r="E112" s="8"/>
@@ -8044,68 +8041,68 @@
       <c r="P112" s="6"/>
       <c r="Q112" s="96"/>
     </row>
-    <row r="113" spans="2:17" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="2:17" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B113" s="86" t="s">
         <v>202</v>
       </c>
       <c r="D113" s="11">
-        <v>17013506.299999997</v>
+        <v>17012904.699999999</v>
       </c>
       <c r="E113" s="11">
-        <v>15654379.699999999</v>
+        <v>15654097.000000004</v>
       </c>
       <c r="F113" s="11">
-        <v>16084400</v>
+        <v>16084435.800000003</v>
       </c>
       <c r="G113" s="11">
-        <v>14141811.800000001</v>
+        <v>14141831.6</v>
       </c>
       <c r="H113" s="11">
-        <v>13702322.699999999</v>
+        <v>13701743.799999997</v>
       </c>
       <c r="I113" s="11">
-        <v>13479632.199999997</v>
+        <v>13477788.599999996</v>
       </c>
       <c r="J113" s="11">
-        <v>14003902.799999999</v>
+        <v>14002557.199999999</v>
       </c>
       <c r="K113" s="11">
-        <v>13723239.999999998</v>
+        <v>13723103.200000003</v>
       </c>
       <c r="L113" s="11">
-        <v>12917857.800000003</v>
+        <v>12917292.700000003</v>
       </c>
       <c r="M113" s="65">
-        <v>14448741.699999999</v>
+        <v>14448439.299999999</v>
       </c>
       <c r="N113" s="11">
-        <v>15443151.300000001</v>
+        <v>15433483.599999998</v>
       </c>
       <c r="O113" s="11">
-        <v>0</v>
+        <v>17464973.899999999</v>
       </c>
       <c r="P113" s="6"/>
       <c r="Q113" s="65">
-        <v>160612946.30000001</v>
-      </c>
-    </row>
-    <row r="114" spans="2:17" x14ac:dyDescent="0.25">
+        <v>178062651.40000001</v>
+      </c>
+    </row>
+    <row r="114" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B114" s="71"/>
     </row>
-    <row r="115" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B115" s="71"/>
     </row>
-    <row r="116" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="116" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B116" s="87" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="117" spans="2:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="2:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B117" s="87" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="118" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="118" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B118" s="87" t="s">
         <v>209</v>
       </c>
